--- a/islami-assistant-web/public/data/قائمة الشركات المعتمدة بداية 2025.xlsx
+++ b/islami-assistant-web/public/data/قائمة الشركات المعتمدة بداية 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BLACK-DIAMOND\Desktop\islami Assistant\islami-assistant-web\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B85D01C-B6F0-45B7-9E04-B6A2B0B96069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF028A0-853E-4368-9B05-E98EE732CB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="4500" windowWidth="21600" windowHeight="10980" xr2:uid="{AC985A7A-9A4F-4839-8FD2-6CB6AA5529A3}"/>
   </bookViews>
@@ -3660,8 +3660,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General\%"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -4007,12 +4008,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -4023,9 +4018,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4041,9 +4033,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4088,9 +4077,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4099,9 +4085,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -4124,14 +4107,14 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4139,28 +4122,46 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4696,41 +4697,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="23.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="62" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="62"/>
+      <c r="D1" s="56"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="63" t="s">
+      <c r="F1" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="63"/>
-      <c r="L1" s="63" t="s">
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="63"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="63"/>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="63"/>
-      <c r="R1" s="63"/>
-      <c r="S1" s="63"/>
-      <c r="T1" s="63" t="s">
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="57"/>
+      <c r="P1" s="57"/>
+      <c r="Q1" s="57"/>
+      <c r="R1" s="57"/>
+      <c r="S1" s="57"/>
+      <c r="T1" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="U1" s="63"/>
-      <c r="V1" s="63"/>
-      <c r="W1" s="63"/>
-      <c r="X1" s="63"/>
-      <c r="Y1" s="63"/>
+      <c r="U1" s="57"/>
+      <c r="V1" s="57"/>
+      <c r="W1" s="57"/>
+      <c r="X1" s="57"/>
+      <c r="Y1" s="57"/>
     </row>
     <row r="2" spans="1:25" ht="31.5">
       <c r="A2" s="4" t="s">
@@ -4820,7 +4821,7 @@
       <c r="D3" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="66"/>
+      <c r="E3" s="58"/>
       <c r="F3" s="10">
         <v>4.25</v>
       </c>
@@ -4893,7 +4894,7 @@
       <c r="D4" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="21"/>
+      <c r="E4" s="59"/>
       <c r="F4" s="15">
         <v>4.25</v>
       </c>
@@ -4968,7 +4969,7 @@
       <c r="D5" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="20"/>
+      <c r="E5" s="60"/>
       <c r="F5" s="15">
         <v>4.25</v>
       </c>
@@ -5041,7 +5042,7 @@
       <c r="D6" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="21"/>
+      <c r="E6" s="59"/>
       <c r="F6" s="15">
         <v>4.25</v>
       </c>
@@ -5114,7 +5115,7 @@
       <c r="D7" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="20"/>
+      <c r="E7" s="60"/>
       <c r="F7" s="15">
         <v>4.25</v>
       </c>
@@ -5187,7 +5188,7 @@
       <c r="D8" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="21"/>
+      <c r="E8" s="59"/>
       <c r="F8" s="15">
         <v>4.25</v>
       </c>
@@ -5260,7 +5261,7 @@
       <c r="D9" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="21"/>
+      <c r="E9" s="59"/>
       <c r="F9" s="15">
         <v>4.25</v>
       </c>
@@ -5323,17 +5324,17 @@
       </c>
     </row>
     <row r="10" spans="1:25" ht="20.25">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="24" t="s">
+      <c r="B10" s="21"/>
+      <c r="C10" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="61">
         <v>45989</v>
       </c>
       <c r="F10" s="15">
@@ -5342,7 +5343,7 @@
       <c r="G10" s="15">
         <v>3.99</v>
       </c>
-      <c r="H10" s="27" t="s">
+      <c r="H10" s="24" t="s">
         <v>39</v>
       </c>
       <c r="I10" s="15">
@@ -5351,7 +5352,7 @@
       <c r="J10" s="15">
         <v>4.5</v>
       </c>
-      <c r="K10" s="27" t="s">
+      <c r="K10" s="24" t="s">
         <v>39</v>
       </c>
       <c r="L10" s="15">
@@ -5398,19 +5399,19 @@
       </c>
     </row>
     <row r="11" spans="1:25" ht="20.25">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C11" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="D11" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="62">
         <v>46090</v>
       </c>
       <c r="F11" s="15">
@@ -5422,13 +5423,13 @@
       <c r="H11" s="15">
         <v>4.25</v>
       </c>
-      <c r="I11" s="27" t="s">
+      <c r="I11" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="J11" s="27" t="s">
+      <c r="J11" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="K11" s="27" t="s">
+      <c r="K11" s="24" t="s">
         <v>39</v>
       </c>
       <c r="L11" s="15">
@@ -5440,37 +5441,37 @@
       <c r="N11" s="15">
         <v>4.5</v>
       </c>
-      <c r="O11" s="27" t="s">
+      <c r="O11" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="P11" s="27" t="s">
+      <c r="P11" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="Q11" s="27" t="s">
+      <c r="Q11" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="R11" s="27" t="s">
+      <c r="R11" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="S11" s="27" t="s">
+      <c r="S11" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="T11" s="27">
+      <c r="T11" s="24">
         <v>4</v>
       </c>
-      <c r="U11" s="27">
+      <c r="U11" s="24">
         <v>4.5</v>
       </c>
-      <c r="V11" s="27">
+      <c r="V11" s="24">
         <v>4.99</v>
       </c>
-      <c r="W11" s="27" t="s">
+      <c r="W11" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="X11" s="27" t="s">
+      <c r="X11" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="Y11" s="27" t="s">
+      <c r="Y11" s="24" t="s">
         <v>39</v>
       </c>
     </row>
@@ -5485,7 +5486,7 @@
       <c r="D12" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="20"/>
+      <c r="E12" s="60"/>
       <c r="F12" s="15">
         <v>4.25</v>
       </c>
@@ -5558,7 +5559,7 @@
       <c r="D13" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="21"/>
+      <c r="E13" s="59"/>
       <c r="F13" s="15">
         <v>4.25</v>
       </c>
@@ -5631,7 +5632,7 @@
       <c r="D14" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="21"/>
+      <c r="E14" s="59"/>
       <c r="F14" s="15">
         <v>4.25</v>
       </c>
@@ -5704,7 +5705,7 @@
       <c r="D15" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="20"/>
+      <c r="E15" s="60"/>
       <c r="F15" s="15">
         <v>4.25</v>
       </c>
@@ -5777,7 +5778,7 @@
       <c r="D16" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E16" s="21"/>
+      <c r="E16" s="59"/>
       <c r="F16" s="15">
         <v>4.25</v>
       </c>
@@ -5850,7 +5851,7 @@
       <c r="D17" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="20"/>
+      <c r="E17" s="60"/>
       <c r="F17" s="15">
         <v>4.25</v>
       </c>
@@ -5923,7 +5924,7 @@
       <c r="D18" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E18" s="21"/>
+      <c r="E18" s="59"/>
       <c r="F18" s="15">
         <v>4.25</v>
       </c>
@@ -5996,7 +5997,7 @@
       <c r="D19" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="20"/>
+      <c r="E19" s="60"/>
       <c r="F19" s="15">
         <v>4.25</v>
       </c>
@@ -6069,7 +6070,7 @@
       <c r="D20" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="21"/>
+      <c r="E20" s="59"/>
       <c r="F20" s="15">
         <v>4.25</v>
       </c>
@@ -6142,7 +6143,7 @@
       <c r="D21" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="20"/>
+      <c r="E21" s="60"/>
       <c r="F21" s="15">
         <v>4.25</v>
       </c>
@@ -6215,7 +6216,7 @@
       <c r="D22" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="21"/>
+      <c r="E22" s="59"/>
       <c r="F22" s="15">
         <v>4.25</v>
       </c>
@@ -6288,7 +6289,7 @@
       <c r="D23" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E23" s="20"/>
+      <c r="E23" s="60"/>
       <c r="F23" s="15">
         <v>4.25</v>
       </c>
@@ -6361,7 +6362,7 @@
       <c r="D24" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E24" s="21"/>
+      <c r="E24" s="59"/>
       <c r="F24" s="15">
         <v>4.25</v>
       </c>
@@ -6434,7 +6435,7 @@
       <c r="D25" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E25" s="20"/>
+      <c r="E25" s="60"/>
       <c r="F25" s="15">
         <v>4.25</v>
       </c>
@@ -6507,7 +6508,7 @@
       <c r="D26" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E26" s="21"/>
+      <c r="E26" s="59"/>
       <c r="F26" s="15">
         <v>4.25</v>
       </c>
@@ -6580,7 +6581,7 @@
       <c r="D27" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E27" s="20"/>
+      <c r="E27" s="60"/>
       <c r="F27" s="15">
         <v>4.25</v>
       </c>
@@ -6653,7 +6654,7 @@
       <c r="D28" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E28" s="21"/>
+      <c r="E28" s="59"/>
       <c r="F28" s="15">
         <v>4.25</v>
       </c>
@@ -6726,7 +6727,7 @@
       <c r="D29" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E29" s="20"/>
+      <c r="E29" s="60"/>
       <c r="F29" s="15">
         <v>4.25</v>
       </c>
@@ -6799,7 +6800,7 @@
       <c r="D30" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="21"/>
+      <c r="E30" s="59"/>
       <c r="F30" s="15">
         <v>4.25</v>
       </c>
@@ -6872,7 +6873,7 @@
       <c r="D31" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E31" s="20"/>
+      <c r="E31" s="60"/>
       <c r="F31" s="15">
         <v>4.25</v>
       </c>
@@ -6945,7 +6946,7 @@
       <c r="D32" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E32" s="21"/>
+      <c r="E32" s="59"/>
       <c r="F32" s="15">
         <v>4.25</v>
       </c>
@@ -7018,7 +7019,7 @@
       <c r="D33" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E33" s="20"/>
+      <c r="E33" s="60"/>
       <c r="F33" s="15">
         <v>4.25</v>
       </c>
@@ -7091,7 +7092,7 @@
       <c r="D34" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E34" s="21"/>
+      <c r="E34" s="59"/>
       <c r="F34" s="15">
         <v>4.25</v>
       </c>
@@ -7164,7 +7165,7 @@
       <c r="D35" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E35" s="20"/>
+      <c r="E35" s="60"/>
       <c r="F35" s="15">
         <v>4.25</v>
       </c>
@@ -7237,7 +7238,7 @@
       <c r="D36" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E36" s="21"/>
+      <c r="E36" s="59"/>
       <c r="F36" s="15">
         <v>4.25</v>
       </c>
@@ -7310,7 +7311,7 @@
       <c r="D37" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E37" s="20"/>
+      <c r="E37" s="60"/>
       <c r="F37" s="15">
         <v>4.25</v>
       </c>
@@ -7383,7 +7384,7 @@
       <c r="D38" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E38" s="21"/>
+      <c r="E38" s="59"/>
       <c r="F38" s="15">
         <v>4.25</v>
       </c>
@@ -7456,7 +7457,7 @@
       <c r="D39" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E39" s="20"/>
+      <c r="E39" s="60"/>
       <c r="F39" s="15">
         <v>4.25</v>
       </c>
@@ -7529,7 +7530,7 @@
       <c r="D40" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E40" s="21"/>
+      <c r="E40" s="59"/>
       <c r="F40" s="15">
         <v>4.25</v>
       </c>
@@ -7602,7 +7603,7 @@
       <c r="D41" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E41" s="20"/>
+      <c r="E41" s="60"/>
       <c r="F41" s="15">
         <v>4.25</v>
       </c>
@@ -7675,7 +7676,7 @@
       <c r="D42" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E42" s="21"/>
+      <c r="E42" s="59"/>
       <c r="F42" s="15">
         <v>4.25</v>
       </c>
@@ -7748,7 +7749,7 @@
       <c r="D43" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E43" s="20"/>
+      <c r="E43" s="60"/>
       <c r="F43" s="15">
         <v>4.25</v>
       </c>
@@ -7821,7 +7822,7 @@
       <c r="D44" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E44" s="21"/>
+      <c r="E44" s="59"/>
       <c r="F44" s="15">
         <v>4.25</v>
       </c>
@@ -7894,7 +7895,7 @@
       <c r="D45" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E45" s="20"/>
+      <c r="E45" s="60"/>
       <c r="F45" s="15">
         <v>4.25</v>
       </c>
@@ -7967,7 +7968,7 @@
       <c r="D46" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E46" s="21"/>
+      <c r="E46" s="59"/>
       <c r="F46" s="15">
         <v>4.25</v>
       </c>
@@ -8040,7 +8041,7 @@
       <c r="D47" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E47" s="20"/>
+      <c r="E47" s="60"/>
       <c r="F47" s="15">
         <v>4.25</v>
       </c>
@@ -8113,7 +8114,7 @@
       <c r="D48" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E48" s="21"/>
+      <c r="E48" s="59"/>
       <c r="F48" s="15">
         <v>4.25</v>
       </c>
@@ -8186,7 +8187,7 @@
       <c r="D49" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E49" s="20"/>
+      <c r="E49" s="60"/>
       <c r="F49" s="15">
         <v>4.25</v>
       </c>
@@ -8259,7 +8260,7 @@
       <c r="D50" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E50" s="21"/>
+      <c r="E50" s="59"/>
       <c r="F50" s="15">
         <v>4.25</v>
       </c>
@@ -8332,7 +8333,7 @@
       <c r="D51" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E51" s="20"/>
+      <c r="E51" s="60"/>
       <c r="F51" s="15">
         <v>4.25</v>
       </c>
@@ -8405,7 +8406,7 @@
       <c r="D52" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E52" s="21"/>
+      <c r="E52" s="59"/>
       <c r="F52" s="15">
         <v>4.25</v>
       </c>
@@ -8478,7 +8479,7 @@
       <c r="D53" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E53" s="20"/>
+      <c r="E53" s="60"/>
       <c r="F53" s="15">
         <v>4.25</v>
       </c>
@@ -8551,7 +8552,7 @@
       <c r="D54" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E54" s="21"/>
+      <c r="E54" s="59"/>
       <c r="F54" s="15">
         <v>4.25</v>
       </c>
@@ -8624,7 +8625,7 @@
       <c r="D55" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E55" s="20"/>
+      <c r="E55" s="60"/>
       <c r="F55" s="15">
         <v>4.25</v>
       </c>
@@ -8697,7 +8698,7 @@
       <c r="D56" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E56" s="21"/>
+      <c r="E56" s="59"/>
       <c r="F56" s="15">
         <v>4.25</v>
       </c>
@@ -8770,7 +8771,7 @@
       <c r="D57" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E57" s="20"/>
+      <c r="E57" s="60"/>
       <c r="F57" s="15">
         <v>4.25</v>
       </c>
@@ -8843,7 +8844,7 @@
       <c r="D58" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E58" s="21"/>
+      <c r="E58" s="59"/>
       <c r="F58" s="15">
         <v>4.25</v>
       </c>
@@ -8916,7 +8917,7 @@
       <c r="D59" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E59" s="20"/>
+      <c r="E59" s="60"/>
       <c r="F59" s="15">
         <v>4.25</v>
       </c>
@@ -8989,7 +8990,7 @@
       <c r="D60" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E60" s="21"/>
+      <c r="E60" s="59"/>
       <c r="F60" s="15">
         <v>4.25</v>
       </c>
@@ -9062,7 +9063,7 @@
       <c r="D61" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E61" s="20"/>
+      <c r="E61" s="60"/>
       <c r="F61" s="15">
         <v>4.25</v>
       </c>
@@ -9135,7 +9136,7 @@
       <c r="D62" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E62" s="21"/>
+      <c r="E62" s="59"/>
       <c r="F62" s="15">
         <v>4.25</v>
       </c>
@@ -9208,7 +9209,7 @@
       <c r="D63" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E63" s="20"/>
+      <c r="E63" s="60"/>
       <c r="F63" s="15">
         <v>4.25</v>
       </c>
@@ -9281,7 +9282,7 @@
       <c r="D64" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E64" s="21"/>
+      <c r="E64" s="59"/>
       <c r="F64" s="15">
         <v>4.25</v>
       </c>
@@ -9354,7 +9355,7 @@
       <c r="D65" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E65" s="20"/>
+      <c r="E65" s="60"/>
       <c r="F65" s="15">
         <v>4.25</v>
       </c>
@@ -9427,7 +9428,7 @@
       <c r="D66" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E66" s="21"/>
+      <c r="E66" s="59"/>
       <c r="F66" s="15">
         <v>4.25</v>
       </c>
@@ -9500,7 +9501,7 @@
       <c r="D67" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E67" s="20"/>
+      <c r="E67" s="60"/>
       <c r="F67" s="15">
         <v>4.25</v>
       </c>
@@ -9573,7 +9574,7 @@
       <c r="D68" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E68" s="21"/>
+      <c r="E68" s="59"/>
       <c r="F68" s="15">
         <v>4.25</v>
       </c>
@@ -9646,7 +9647,7 @@
       <c r="D69" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E69" s="20"/>
+      <c r="E69" s="60"/>
       <c r="F69" s="15">
         <v>4.25</v>
       </c>
@@ -9719,7 +9720,7 @@
       <c r="D70" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E70" s="21"/>
+      <c r="E70" s="59"/>
       <c r="F70" s="15">
         <v>4.25</v>
       </c>
@@ -9792,7 +9793,7 @@
       <c r="D71" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E71" s="20"/>
+      <c r="E71" s="60"/>
       <c r="F71" s="15">
         <v>4.25</v>
       </c>
@@ -9865,7 +9866,7 @@
       <c r="D72" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E72" s="21"/>
+      <c r="E72" s="59"/>
       <c r="F72" s="15">
         <v>4.25</v>
       </c>
@@ -9938,7 +9939,7 @@
       <c r="D73" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E73" s="20"/>
+      <c r="E73" s="60"/>
       <c r="F73" s="15">
         <v>4.25</v>
       </c>
@@ -10011,7 +10012,7 @@
       <c r="D74" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E74" s="21"/>
+      <c r="E74" s="59"/>
       <c r="F74" s="15">
         <v>4.25</v>
       </c>
@@ -10084,7 +10085,7 @@
       <c r="D75" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E75" s="20"/>
+      <c r="E75" s="60"/>
       <c r="F75" s="15">
         <v>4.25</v>
       </c>
@@ -10157,7 +10158,7 @@
       <c r="D76" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E76" s="21"/>
+      <c r="E76" s="59"/>
       <c r="F76" s="15">
         <v>4.25</v>
       </c>
@@ -10230,7 +10231,7 @@
       <c r="D77" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E77" s="20"/>
+      <c r="E77" s="60"/>
       <c r="F77" s="15">
         <v>4.25</v>
       </c>
@@ -10303,7 +10304,7 @@
       <c r="D78" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E78" s="21"/>
+      <c r="E78" s="59"/>
       <c r="F78" s="15">
         <v>4.25</v>
       </c>
@@ -10376,7 +10377,7 @@
       <c r="D79" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E79" s="20"/>
+      <c r="E79" s="60"/>
       <c r="F79" s="15">
         <v>4.25</v>
       </c>
@@ -10449,7 +10450,7 @@
       <c r="D80" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E80" s="21"/>
+      <c r="E80" s="59"/>
       <c r="F80" s="15">
         <v>4.25</v>
       </c>
@@ -10522,7 +10523,7 @@
       <c r="D81" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E81" s="20"/>
+      <c r="E81" s="60"/>
       <c r="F81" s="15">
         <v>4.25</v>
       </c>
@@ -10595,7 +10596,7 @@
       <c r="D82" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E82" s="21"/>
+      <c r="E82" s="59"/>
       <c r="F82" s="15">
         <v>4.25</v>
       </c>
@@ -10668,7 +10669,7 @@
       <c r="D83" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E83" s="20"/>
+      <c r="E83" s="60"/>
       <c r="F83" s="15">
         <v>4.25</v>
       </c>
@@ -10741,7 +10742,7 @@
       <c r="D84" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E84" s="21"/>
+      <c r="E84" s="59"/>
       <c r="F84" s="15">
         <v>4.25</v>
       </c>
@@ -10814,7 +10815,7 @@
       <c r="D85" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E85" s="20"/>
+      <c r="E85" s="60"/>
       <c r="F85" s="15">
         <v>4.25</v>
       </c>
@@ -10887,7 +10888,7 @@
       <c r="D86" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E86" s="21"/>
+      <c r="E86" s="59"/>
       <c r="F86" s="15">
         <v>4.25</v>
       </c>
@@ -10960,7 +10961,7 @@
       <c r="D87" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E87" s="20"/>
+      <c r="E87" s="60"/>
       <c r="F87" s="15">
         <v>4.25</v>
       </c>
@@ -11033,7 +11034,7 @@
       <c r="D88" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E88" s="21"/>
+      <c r="E88" s="59"/>
       <c r="F88" s="15">
         <v>4.25</v>
       </c>
@@ -11106,7 +11107,7 @@
       <c r="D89" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E89" s="20"/>
+      <c r="E89" s="60"/>
       <c r="F89" s="15">
         <v>4.25</v>
       </c>
@@ -11179,7 +11180,7 @@
       <c r="D90" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E90" s="21"/>
+      <c r="E90" s="59"/>
       <c r="F90" s="15">
         <v>4.25</v>
       </c>
@@ -11252,7 +11253,7 @@
       <c r="D91" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E91" s="20"/>
+      <c r="E91" s="60"/>
       <c r="F91" s="15">
         <v>4.25</v>
       </c>
@@ -11325,7 +11326,7 @@
       <c r="D92" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="E92" s="20" t="s">
+      <c r="E92" s="60" t="s">
         <v>125</v>
       </c>
       <c r="F92" s="15">
@@ -11400,7 +11401,7 @@
       <c r="D93" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E93" s="21"/>
+      <c r="E93" s="59"/>
       <c r="F93" s="15">
         <v>4.25</v>
       </c>
@@ -11473,7 +11474,7 @@
       <c r="D94" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E94" s="20"/>
+      <c r="E94" s="60"/>
       <c r="F94" s="15">
         <v>4.25</v>
       </c>
@@ -11546,7 +11547,7 @@
       <c r="D95" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E95" s="21"/>
+      <c r="E95" s="59"/>
       <c r="F95" s="15">
         <v>4.25</v>
       </c>
@@ -11619,7 +11620,7 @@
       <c r="D96" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E96" s="20"/>
+      <c r="E96" s="60"/>
       <c r="F96" s="15">
         <v>4.25</v>
       </c>
@@ -11692,7 +11693,7 @@
       <c r="D97" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E97" s="21"/>
+      <c r="E97" s="59"/>
       <c r="F97" s="15">
         <v>4.25</v>
       </c>
@@ -11765,7 +11766,7 @@
       <c r="D98" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E98" s="20"/>
+      <c r="E98" s="60"/>
       <c r="F98" s="15">
         <v>4.25</v>
       </c>
@@ -11838,7 +11839,7 @@
       <c r="D99" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E99" s="21"/>
+      <c r="E99" s="59"/>
       <c r="F99" s="15">
         <v>4.25</v>
       </c>
@@ -11911,7 +11912,7 @@
       <c r="D100" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E100" s="20"/>
+      <c r="E100" s="60"/>
       <c r="F100" s="15">
         <v>4.25</v>
       </c>
@@ -11984,7 +11985,7 @@
       <c r="D101" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E101" s="21"/>
+      <c r="E101" s="59"/>
       <c r="F101" s="15">
         <v>4.25</v>
       </c>
@@ -12057,7 +12058,7 @@
       <c r="D102" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E102" s="20"/>
+      <c r="E102" s="60"/>
       <c r="F102" s="15">
         <v>4.25</v>
       </c>
@@ -12130,7 +12131,7 @@
       <c r="D103" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E103" s="21"/>
+      <c r="E103" s="59"/>
       <c r="F103" s="15">
         <v>4.25</v>
       </c>
@@ -12203,7 +12204,7 @@
       <c r="D104" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E104" s="20"/>
+      <c r="E104" s="60"/>
       <c r="F104" s="15">
         <v>4.25</v>
       </c>
@@ -12276,7 +12277,7 @@
       <c r="D105" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E105" s="21"/>
+      <c r="E105" s="59"/>
       <c r="F105" s="15">
         <v>4.25</v>
       </c>
@@ -12349,7 +12350,7 @@
       <c r="D106" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E106" s="20"/>
+      <c r="E106" s="60"/>
       <c r="F106" s="15">
         <v>4.25</v>
       </c>
@@ -12422,7 +12423,7 @@
       <c r="D107" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E107" s="21"/>
+      <c r="E107" s="59"/>
       <c r="F107" s="15">
         <v>4.25</v>
       </c>
@@ -12495,7 +12496,7 @@
       <c r="D108" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E108" s="20"/>
+      <c r="E108" s="60"/>
       <c r="F108" s="15">
         <v>4.25</v>
       </c>
@@ -12568,7 +12569,7 @@
       <c r="D109" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E109" s="21"/>
+      <c r="E109" s="59"/>
       <c r="F109" s="15">
         <v>4.25</v>
       </c>
@@ -12641,7 +12642,7 @@
       <c r="D110" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E110" s="20"/>
+      <c r="E110" s="60"/>
       <c r="F110" s="15">
         <v>4.25</v>
       </c>
@@ -12714,7 +12715,7 @@
       <c r="D111" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E111" s="21"/>
+      <c r="E111" s="59"/>
       <c r="F111" s="15">
         <v>4.25</v>
       </c>
@@ -12787,7 +12788,7 @@
       <c r="D112" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E112" s="20"/>
+      <c r="E112" s="60"/>
       <c r="F112" s="15">
         <v>4.25</v>
       </c>
@@ -12860,7 +12861,7 @@
       <c r="D113" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E113" s="21"/>
+      <c r="E113" s="59"/>
       <c r="F113" s="15">
         <v>4.25</v>
       </c>
@@ -12933,7 +12934,7 @@
       <c r="D114" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E114" s="20"/>
+      <c r="E114" s="60"/>
       <c r="F114" s="15">
         <v>4.25</v>
       </c>
@@ -13006,7 +13007,7 @@
       <c r="D115" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E115" s="21"/>
+      <c r="E115" s="59"/>
       <c r="F115" s="15">
         <v>4.25</v>
       </c>
@@ -13079,7 +13080,7 @@
       <c r="D116" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E116" s="20"/>
+      <c r="E116" s="60"/>
       <c r="F116" s="15">
         <v>4.25</v>
       </c>
@@ -13152,7 +13153,7 @@
       <c r="D117" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E117" s="21"/>
+      <c r="E117" s="59"/>
       <c r="F117" s="15">
         <v>4.25</v>
       </c>
@@ -13225,7 +13226,7 @@
       <c r="D118" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E118" s="20"/>
+      <c r="E118" s="60"/>
       <c r="F118" s="15">
         <v>4.25</v>
       </c>
@@ -13298,7 +13299,7 @@
       <c r="D119" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E119" s="21"/>
+      <c r="E119" s="59"/>
       <c r="F119" s="15">
         <v>4.25</v>
       </c>
@@ -13371,7 +13372,7 @@
       <c r="D120" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E120" s="20"/>
+      <c r="E120" s="60"/>
       <c r="F120" s="15">
         <v>4.25</v>
       </c>
@@ -13444,7 +13445,7 @@
       <c r="D121" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E121" s="21"/>
+      <c r="E121" s="59"/>
       <c r="F121" s="15">
         <v>4.25</v>
       </c>
@@ -13517,7 +13518,7 @@
       <c r="D122" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E122" s="20"/>
+      <c r="E122" s="60"/>
       <c r="F122" s="15">
         <v>4.25</v>
       </c>
@@ -13590,7 +13591,7 @@
       <c r="D123" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E123" s="21"/>
+      <c r="E123" s="59"/>
       <c r="F123" s="15">
         <v>4.25</v>
       </c>
@@ -13663,7 +13664,7 @@
       <c r="D124" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E124" s="20"/>
+      <c r="E124" s="60"/>
       <c r="F124" s="15">
         <v>4.25</v>
       </c>
@@ -13736,7 +13737,7 @@
       <c r="D125" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E125" s="21"/>
+      <c r="E125" s="59"/>
       <c r="F125" s="15">
         <v>4.25</v>
       </c>
@@ -13809,7 +13810,7 @@
       <c r="D126" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E126" s="20"/>
+      <c r="E126" s="60"/>
       <c r="F126" s="15">
         <v>4.25</v>
       </c>
@@ -13882,7 +13883,7 @@
       <c r="D127" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E127" s="21"/>
+      <c r="E127" s="59"/>
       <c r="F127" s="15">
         <v>4.25</v>
       </c>
@@ -13955,7 +13956,7 @@
       <c r="D128" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E128" s="20"/>
+      <c r="E128" s="60"/>
       <c r="F128" s="15">
         <v>4.25</v>
       </c>
@@ -14028,7 +14029,7 @@
       <c r="D129" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E129" s="21"/>
+      <c r="E129" s="59"/>
       <c r="F129" s="15">
         <v>4.25</v>
       </c>
@@ -14101,7 +14102,7 @@
       <c r="D130" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E130" s="20"/>
+      <c r="E130" s="60"/>
       <c r="F130" s="15">
         <v>4.25</v>
       </c>
@@ -14174,7 +14175,7 @@
       <c r="D131" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E131" s="21"/>
+      <c r="E131" s="59"/>
       <c r="F131" s="15">
         <v>4.25</v>
       </c>
@@ -14237,17 +14238,17 @@
       </c>
     </row>
     <row r="132" spans="1:25" ht="20.25">
-      <c r="A132" s="22" t="s">
+      <c r="A132" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="B132" s="23"/>
-      <c r="C132" s="24" t="s">
+      <c r="B132" s="21"/>
+      <c r="C132" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="D132" s="25" t="s">
+      <c r="D132" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="E132" s="26"/>
+      <c r="E132" s="61"/>
       <c r="F132" s="15">
         <v>4.25</v>
       </c>
@@ -14310,17 +14311,17 @@
       </c>
     </row>
     <row r="133" spans="1:25" ht="20.25">
-      <c r="A133" s="28" t="s">
+      <c r="A133" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="B133" s="29"/>
-      <c r="C133" s="30" t="s">
+      <c r="B133" s="26"/>
+      <c r="C133" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="D133" s="31" t="s">
+      <c r="D133" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="E133" s="32"/>
+      <c r="E133" s="62"/>
       <c r="F133" s="15">
         <v>4.25</v>
       </c>
@@ -14383,17 +14384,17 @@
       </c>
     </row>
     <row r="134" spans="1:25" ht="20.25">
-      <c r="A134" s="22" t="s">
+      <c r="A134" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="B134" s="23"/>
-      <c r="C134" s="24" t="s">
+      <c r="B134" s="21"/>
+      <c r="C134" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="D134" s="25" t="s">
+      <c r="D134" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="E134" s="26"/>
+      <c r="E134" s="61"/>
       <c r="F134" s="15">
         <v>4.25</v>
       </c>
@@ -14456,19 +14457,19 @@
       </c>
     </row>
     <row r="135" spans="1:25" ht="25.5">
-      <c r="A135" s="28" t="s">
+      <c r="A135" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="B135" s="33" t="s">
+      <c r="B135" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="C135" s="30" t="s">
+      <c r="C135" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="D135" s="31" t="s">
+      <c r="D135" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="E135" s="32"/>
+      <c r="E135" s="62"/>
       <c r="F135" s="15">
         <v>4.25</v>
       </c>
@@ -14531,17 +14532,17 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="20.25">
-      <c r="A136" s="22" t="s">
+      <c r="A136" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="B136" s="23"/>
-      <c r="C136" s="24" t="s">
+      <c r="B136" s="21"/>
+      <c r="C136" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="D136" s="25" t="s">
+      <c r="D136" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="E136" s="26"/>
+      <c r="E136" s="61"/>
       <c r="F136" s="15">
         <v>4.25</v>
       </c>
@@ -14614,7 +14615,7 @@
       <c r="D137" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E137" s="20"/>
+      <c r="E137" s="60"/>
       <c r="F137" s="15">
         <v>4.25</v>
       </c>
@@ -14689,7 +14690,7 @@
       <c r="D138" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E138" s="21"/>
+      <c r="E138" s="59"/>
       <c r="F138" s="15">
         <v>4.25</v>
       </c>
@@ -14762,7 +14763,7 @@
       <c r="D139" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E139" s="20"/>
+      <c r="E139" s="60"/>
       <c r="F139" s="15">
         <v>4.25</v>
       </c>
@@ -14828,16 +14829,16 @@
       <c r="A140" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="B140" s="33" t="s">
+      <c r="B140" s="29" t="s">
         <v>176</v>
       </c>
       <c r="C140" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D140" s="31" t="s">
+      <c r="D140" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E140" s="21">
+      <c r="E140" s="59">
         <v>46022</v>
       </c>
       <c r="F140" s="15">
@@ -14912,7 +14913,7 @@
       <c r="D141" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E141" s="21"/>
+      <c r="E141" s="59"/>
       <c r="F141" s="15">
         <v>4.25</v>
       </c>
@@ -14985,7 +14986,7 @@
       <c r="D142" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E142" s="20"/>
+      <c r="E142" s="60"/>
       <c r="F142" s="15">
         <v>4.25</v>
       </c>
@@ -15058,7 +15059,7 @@
       <c r="D143" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E143" s="21"/>
+      <c r="E143" s="59"/>
       <c r="F143" s="15">
         <v>4.25</v>
       </c>
@@ -15131,7 +15132,7 @@
       <c r="D144" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E144" s="20"/>
+      <c r="E144" s="60"/>
       <c r="F144" s="15">
         <v>4.25</v>
       </c>
@@ -15204,7 +15205,7 @@
       <c r="D145" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E145" s="21"/>
+      <c r="E145" s="59"/>
       <c r="F145" s="15">
         <v>4.25</v>
       </c>
@@ -15277,7 +15278,7 @@
       <c r="D146" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E146" s="20"/>
+      <c r="E146" s="60"/>
       <c r="F146" s="15">
         <v>4.25</v>
       </c>
@@ -15350,7 +15351,7 @@
       <c r="D147" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E147" s="21"/>
+      <c r="E147" s="59"/>
       <c r="F147" s="15">
         <v>4.25</v>
       </c>
@@ -15423,7 +15424,7 @@
       <c r="D148" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E148" s="20"/>
+      <c r="E148" s="60"/>
       <c r="F148" s="15">
         <v>4.25</v>
       </c>
@@ -15496,7 +15497,7 @@
       <c r="D149" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E149" s="21"/>
+      <c r="E149" s="59"/>
       <c r="F149" s="15">
         <v>4.25</v>
       </c>
@@ -15569,7 +15570,7 @@
       <c r="D150" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E150" s="20"/>
+      <c r="E150" s="60"/>
       <c r="F150" s="15">
         <v>4.25</v>
       </c>
@@ -15642,7 +15643,7 @@
       <c r="D151" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E151" s="20"/>
+      <c r="E151" s="60"/>
       <c r="F151" s="15">
         <v>4.25</v>
       </c>
@@ -15715,7 +15716,7 @@
       <c r="D152" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E152" s="21"/>
+      <c r="E152" s="59"/>
       <c r="F152" s="15">
         <v>4.25</v>
       </c>
@@ -15788,7 +15789,7 @@
       <c r="D153" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E153" s="20"/>
+      <c r="E153" s="60"/>
       <c r="F153" s="15">
         <v>4.25</v>
       </c>
@@ -15861,7 +15862,7 @@
       <c r="D154" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E154" s="21"/>
+      <c r="E154" s="59"/>
       <c r="F154" s="15">
         <v>4.25</v>
       </c>
@@ -15934,7 +15935,7 @@
       <c r="D155" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E155" s="20"/>
+      <c r="E155" s="60"/>
       <c r="F155" s="15">
         <v>4.25</v>
       </c>
@@ -16007,7 +16008,7 @@
       <c r="D156" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E156" s="20"/>
+      <c r="E156" s="60"/>
       <c r="F156" s="15">
         <v>4.25</v>
       </c>
@@ -16080,7 +16081,7 @@
       <c r="D157" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E157" s="21"/>
+      <c r="E157" s="59"/>
       <c r="F157" s="15">
         <v>4.25</v>
       </c>
@@ -16153,7 +16154,7 @@
       <c r="D158" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E158" s="20"/>
+      <c r="E158" s="60"/>
       <c r="F158" s="15">
         <v>4.25</v>
       </c>
@@ -16226,7 +16227,7 @@
       <c r="D159" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E159" s="21"/>
+      <c r="E159" s="59"/>
       <c r="F159" s="15">
         <v>4.25</v>
       </c>
@@ -16299,7 +16300,7 @@
       <c r="D160" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E160" s="20"/>
+      <c r="E160" s="60"/>
       <c r="F160" s="15">
         <v>4.25</v>
       </c>
@@ -16372,7 +16373,7 @@
       <c r="D161" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E161" s="20"/>
+      <c r="E161" s="60"/>
       <c r="F161" s="15">
         <v>4.25</v>
       </c>
@@ -16445,7 +16446,7 @@
       <c r="D162" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E162" s="21"/>
+      <c r="E162" s="59"/>
       <c r="F162" s="15">
         <v>4.25</v>
       </c>
@@ -16518,7 +16519,7 @@
       <c r="D163" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E163" s="21"/>
+      <c r="E163" s="59"/>
       <c r="F163" s="15">
         <v>4.25</v>
       </c>
@@ -16591,7 +16592,7 @@
       <c r="D164" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E164" s="20"/>
+      <c r="E164" s="60"/>
       <c r="F164" s="15">
         <v>4.25</v>
       </c>
@@ -16664,7 +16665,7 @@
       <c r="D165" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E165" s="21"/>
+      <c r="E165" s="59"/>
       <c r="F165" s="15">
         <v>4.25</v>
       </c>
@@ -16737,7 +16738,7 @@
       <c r="D166" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E166" s="20"/>
+      <c r="E166" s="60"/>
       <c r="F166" s="15">
         <v>4.25</v>
       </c>
@@ -16810,7 +16811,7 @@
       <c r="D167" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E167" s="20"/>
+      <c r="E167" s="60"/>
       <c r="F167" s="15">
         <v>4.25</v>
       </c>
@@ -16883,7 +16884,7 @@
       <c r="D168" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E168" s="21"/>
+      <c r="E168" s="59"/>
       <c r="F168" s="15">
         <v>4.25</v>
       </c>
@@ -16956,7 +16957,7 @@
       <c r="D169" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E169" s="20"/>
+      <c r="E169" s="60"/>
       <c r="F169" s="15">
         <v>4.25</v>
       </c>
@@ -17029,7 +17030,7 @@
       <c r="D170" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E170" s="21"/>
+      <c r="E170" s="59"/>
       <c r="F170" s="15">
         <v>4.25</v>
       </c>
@@ -17102,7 +17103,7 @@
       <c r="D171" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E171" s="20"/>
+      <c r="E171" s="60"/>
       <c r="F171" s="15">
         <v>4.25</v>
       </c>
@@ -17175,7 +17176,7 @@
       <c r="D172" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E172" s="21"/>
+      <c r="E172" s="59"/>
       <c r="F172" s="15">
         <v>4.25</v>
       </c>
@@ -17248,7 +17249,7 @@
       <c r="D173" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E173" s="20"/>
+      <c r="E173" s="60"/>
       <c r="F173" s="15">
         <v>4.25</v>
       </c>
@@ -17321,7 +17322,7 @@
       <c r="D174" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E174" s="21"/>
+      <c r="E174" s="59"/>
       <c r="F174" s="15">
         <v>4.25</v>
       </c>
@@ -17394,7 +17395,7 @@
       <c r="D175" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E175" s="20"/>
+      <c r="E175" s="60"/>
       <c r="F175" s="15">
         <v>4.25</v>
       </c>
@@ -17464,10 +17465,10 @@
       <c r="C176" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D176" s="31" t="s">
+      <c r="D176" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E176" s="21">
+      <c r="E176" s="59">
         <v>46022</v>
       </c>
       <c r="F176" s="15">
@@ -17542,7 +17543,7 @@
       <c r="D177" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E177" s="20"/>
+      <c r="E177" s="60"/>
       <c r="F177" s="15">
         <v>4.25</v>
       </c>
@@ -17615,7 +17616,7 @@
       <c r="D178" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E178" s="21"/>
+      <c r="E178" s="59"/>
       <c r="F178" s="15">
         <v>4.25</v>
       </c>
@@ -17688,7 +17689,7 @@
       <c r="D179" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E179" s="20"/>
+      <c r="E179" s="60"/>
       <c r="F179" s="15">
         <v>4.25</v>
       </c>
@@ -17761,7 +17762,7 @@
       <c r="D180" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E180" s="20"/>
+      <c r="E180" s="60"/>
       <c r="F180" s="15">
         <v>4.25</v>
       </c>
@@ -17834,7 +17835,7 @@
       <c r="D181" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E181" s="21"/>
+      <c r="E181" s="59"/>
       <c r="F181" s="15">
         <v>4.25</v>
       </c>
@@ -17907,7 +17908,7 @@
       <c r="D182" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E182" s="20"/>
+      <c r="E182" s="60"/>
       <c r="F182" s="15">
         <v>4.25</v>
       </c>
@@ -17980,7 +17981,7 @@
       <c r="D183" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E183" s="21"/>
+      <c r="E183" s="59"/>
       <c r="F183" s="15">
         <v>4.25</v>
       </c>
@@ -18053,7 +18054,7 @@
       <c r="D184" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E184" s="20"/>
+      <c r="E184" s="60"/>
       <c r="F184" s="15">
         <v>4.25</v>
       </c>
@@ -18126,7 +18127,7 @@
       <c r="D185" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E185" s="21"/>
+      <c r="E185" s="59"/>
       <c r="F185" s="15">
         <v>4.25</v>
       </c>
@@ -18199,7 +18200,7 @@
       <c r="D186" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E186" s="20"/>
+      <c r="E186" s="60"/>
       <c r="F186" s="15">
         <v>4.25</v>
       </c>
@@ -18272,7 +18273,7 @@
       <c r="D187" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E187" s="21"/>
+      <c r="E187" s="59"/>
       <c r="F187" s="15">
         <v>4.25</v>
       </c>
@@ -18345,7 +18346,7 @@
       <c r="D188" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E188" s="21"/>
+      <c r="E188" s="59"/>
       <c r="F188" s="15">
         <v>4.25</v>
       </c>
@@ -18418,7 +18419,7 @@
       <c r="D189" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E189" s="21"/>
+      <c r="E189" s="59"/>
       <c r="F189" s="15">
         <v>4.25</v>
       </c>
@@ -18491,7 +18492,7 @@
       <c r="D190" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E190" s="20"/>
+      <c r="E190" s="60"/>
       <c r="F190" s="15">
         <v>4.25</v>
       </c>
@@ -18564,7 +18565,7 @@
       <c r="D191" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E191" s="21"/>
+      <c r="E191" s="59"/>
       <c r="F191" s="15">
         <v>4.25</v>
       </c>
@@ -18637,7 +18638,7 @@
       <c r="D192" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E192" s="20"/>
+      <c r="E192" s="60"/>
       <c r="F192" s="15">
         <v>4.25</v>
       </c>
@@ -18710,7 +18711,7 @@
       <c r="D193" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E193" s="21"/>
+      <c r="E193" s="59"/>
       <c r="F193" s="15">
         <v>4.25</v>
       </c>
@@ -18783,7 +18784,7 @@
       <c r="D194" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E194" s="20"/>
+      <c r="E194" s="60"/>
       <c r="F194" s="15">
         <v>4.25</v>
       </c>
@@ -18856,7 +18857,7 @@
       <c r="D195" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E195" s="21"/>
+      <c r="E195" s="59"/>
       <c r="F195" s="15">
         <v>4.25</v>
       </c>
@@ -18929,7 +18930,7 @@
       <c r="D196" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E196" s="21"/>
+      <c r="E196" s="59"/>
       <c r="F196" s="15">
         <v>4.25</v>
       </c>
@@ -19002,7 +19003,7 @@
       <c r="D197" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E197" s="20"/>
+      <c r="E197" s="60"/>
       <c r="F197" s="15">
         <v>4.25</v>
       </c>
@@ -19075,7 +19076,7 @@
       <c r="D198" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E198" s="21"/>
+      <c r="E198" s="59"/>
       <c r="F198" s="15">
         <v>4.25</v>
       </c>
@@ -19138,19 +19139,19 @@
       </c>
     </row>
     <row r="199" spans="1:25" ht="38.25">
-      <c r="A199" s="28" t="s">
+      <c r="A199" s="25" t="s">
         <v>235</v>
       </c>
-      <c r="B199" s="33" t="s">
+      <c r="B199" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="C199" s="30" t="s">
+      <c r="C199" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D199" s="31" t="s">
+      <c r="D199" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="E199" s="32"/>
+      <c r="E199" s="62"/>
       <c r="F199" s="15">
         <v>4.25</v>
       </c>
@@ -19213,19 +19214,19 @@
       </c>
     </row>
     <row r="200" spans="1:25" ht="38.25">
-      <c r="A200" s="22" t="s">
+      <c r="A200" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="B200" s="34" t="s">
+      <c r="B200" s="30" t="s">
         <v>236</v>
       </c>
-      <c r="C200" s="24" t="s">
+      <c r="C200" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D200" s="25" t="s">
+      <c r="D200" s="23" t="s">
         <v>238</v>
       </c>
-      <c r="E200" s="26"/>
+      <c r="E200" s="61"/>
       <c r="F200" s="15">
         <v>4.25</v>
       </c>
@@ -19288,17 +19289,17 @@
       </c>
     </row>
     <row r="201" spans="1:25" ht="38.25">
-      <c r="A201" s="28" t="s">
+      <c r="A201" s="25" t="s">
         <v>239</v>
       </c>
-      <c r="B201" s="29"/>
-      <c r="C201" s="30" t="s">
+      <c r="B201" s="26"/>
+      <c r="C201" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D201" s="31" t="s">
+      <c r="D201" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E201" s="20">
+      <c r="E201" s="60">
         <v>46022</v>
       </c>
       <c r="F201" s="15">
@@ -19370,10 +19371,10 @@
       <c r="C202" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D202" s="31" t="s">
+      <c r="D202" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E202" s="20">
+      <c r="E202" s="60">
         <v>46022</v>
       </c>
       <c r="F202" s="15">
@@ -19438,17 +19439,17 @@
       </c>
     </row>
     <row r="203" spans="1:25" ht="20.25">
-      <c r="A203" s="28" t="s">
+      <c r="A203" s="25" t="s">
         <v>241</v>
       </c>
-      <c r="B203" s="29"/>
-      <c r="C203" s="30" t="s">
+      <c r="B203" s="26"/>
+      <c r="C203" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D203" s="31" t="s">
+      <c r="D203" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="E203" s="32"/>
+      <c r="E203" s="62"/>
       <c r="F203" s="15">
         <v>4.25</v>
       </c>
@@ -19511,17 +19512,17 @@
       </c>
     </row>
     <row r="204" spans="1:25" ht="38.25">
-      <c r="A204" s="22" t="s">
+      <c r="A204" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="B204" s="23"/>
-      <c r="C204" s="24" t="s">
+      <c r="B204" s="21"/>
+      <c r="C204" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D204" s="31" t="s">
+      <c r="D204" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E204" s="26">
+      <c r="E204" s="61">
         <v>46022</v>
       </c>
       <c r="F204" s="15">
@@ -19596,7 +19597,7 @@
       <c r="D205" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E205" s="21"/>
+      <c r="E205" s="59"/>
       <c r="F205" s="15">
         <v>4.25</v>
       </c>
@@ -19671,7 +19672,7 @@
       <c r="D206" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="E206" s="20"/>
+      <c r="E206" s="60"/>
       <c r="F206" s="15">
         <v>4.25</v>
       </c>
@@ -19744,7 +19745,7 @@
       <c r="D207" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E207" s="21"/>
+      <c r="E207" s="59"/>
       <c r="F207" s="15">
         <v>4.25</v>
       </c>
@@ -19817,7 +19818,7 @@
       <c r="D208" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E208" s="20"/>
+      <c r="E208" s="60"/>
       <c r="F208" s="15">
         <v>4.25</v>
       </c>
@@ -19890,7 +19891,7 @@
       <c r="D209" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E209" s="21"/>
+      <c r="E209" s="59"/>
       <c r="F209" s="15">
         <v>4.25</v>
       </c>
@@ -19963,7 +19964,7 @@
       <c r="D210" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E210" s="20"/>
+      <c r="E210" s="60"/>
       <c r="F210" s="15">
         <v>4.25</v>
       </c>
@@ -20036,7 +20037,7 @@
       <c r="D211" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E211" s="21">
+      <c r="E211" s="59">
         <v>45945</v>
       </c>
       <c r="F211" s="15">
@@ -20108,10 +20109,10 @@
       <c r="C212" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D212" s="25" t="s">
+      <c r="D212" s="23" t="s">
         <v>238</v>
       </c>
-      <c r="E212" s="20"/>
+      <c r="E212" s="60"/>
       <c r="F212" s="15">
         <v>4.25</v>
       </c>
@@ -20184,7 +20185,7 @@
       <c r="D213" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E213" s="21">
+      <c r="E213" s="59">
         <v>45966</v>
       </c>
       <c r="F213" s="15">
@@ -20259,7 +20260,7 @@
       <c r="D214" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E214" s="20"/>
+      <c r="E214" s="60"/>
       <c r="F214" s="15">
         <v>4.25</v>
       </c>
@@ -20322,17 +20323,17 @@
       </c>
     </row>
     <row r="215" spans="1:25" ht="20.25">
-      <c r="A215" s="28" t="s">
+      <c r="A215" s="25" t="s">
         <v>253</v>
       </c>
-      <c r="B215" s="29"/>
-      <c r="C215" s="30" t="s">
+      <c r="B215" s="26"/>
+      <c r="C215" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D215" s="31" t="s">
+      <c r="D215" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="E215" s="32"/>
+      <c r="E215" s="62"/>
       <c r="F215" s="15">
         <v>4.25</v>
       </c>
@@ -20395,17 +20396,17 @@
       </c>
     </row>
     <row r="216" spans="1:25" ht="20.25">
-      <c r="A216" s="22" t="s">
+      <c r="A216" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="B216" s="23"/>
-      <c r="C216" s="24" t="s">
+      <c r="B216" s="21"/>
+      <c r="C216" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D216" s="25" t="s">
+      <c r="D216" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="E216" s="26"/>
+      <c r="E216" s="61"/>
       <c r="F216" s="15">
         <v>4.25</v>
       </c>
@@ -20468,17 +20469,17 @@
       </c>
     </row>
     <row r="217" spans="1:25" ht="20.25">
-      <c r="A217" s="28" t="s">
+      <c r="A217" s="25" t="s">
         <v>255</v>
       </c>
-      <c r="B217" s="29"/>
-      <c r="C217" s="30" t="s">
+      <c r="B217" s="26"/>
+      <c r="C217" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D217" s="31" t="s">
+      <c r="D217" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="E217" s="32"/>
+      <c r="E217" s="62"/>
       <c r="F217" s="15">
         <v>4.25</v>
       </c>
@@ -20541,17 +20542,17 @@
       </c>
     </row>
     <row r="218" spans="1:25" ht="20.25">
-      <c r="A218" s="22" t="s">
+      <c r="A218" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="B218" s="23"/>
-      <c r="C218" s="24" t="s">
+      <c r="B218" s="21"/>
+      <c r="C218" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D218" s="25" t="s">
+      <c r="D218" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="E218" s="26"/>
+      <c r="E218" s="61"/>
       <c r="F218" s="15">
         <v>4.25</v>
       </c>
@@ -20614,19 +20615,19 @@
       </c>
     </row>
     <row r="219" spans="1:25" ht="38.25">
-      <c r="A219" s="28" t="s">
+      <c r="A219" s="25" t="s">
         <v>257</v>
       </c>
-      <c r="B219" s="33" t="s">
+      <c r="B219" s="29" t="s">
         <v>176</v>
       </c>
-      <c r="C219" s="30" t="s">
+      <c r="C219" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D219" s="31" t="s">
+      <c r="D219" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E219" s="32">
+      <c r="E219" s="62">
         <v>46022</v>
       </c>
       <c r="F219" s="15">
@@ -20701,7 +20702,7 @@
       <c r="D220" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E220" s="20"/>
+      <c r="E220" s="60"/>
       <c r="F220" s="15">
         <v>4.25</v>
       </c>
@@ -20774,7 +20775,7 @@
       <c r="D221" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E221" s="21"/>
+      <c r="E221" s="59"/>
       <c r="F221" s="15">
         <v>4.25</v>
       </c>
@@ -20837,17 +20838,17 @@
       </c>
     </row>
     <row r="222" spans="1:25" ht="38.25">
-      <c r="A222" s="22" t="s">
+      <c r="A222" s="20" t="s">
         <v>260</v>
       </c>
-      <c r="B222" s="23"/>
-      <c r="C222" s="24" t="s">
+      <c r="B222" s="21"/>
+      <c r="C222" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D222" s="31" t="s">
+      <c r="D222" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E222" s="26">
+      <c r="E222" s="61">
         <v>46022</v>
       </c>
       <c r="F222" s="15">
@@ -20912,19 +20913,19 @@
       </c>
     </row>
     <row r="223" spans="1:25" ht="38.25">
-      <c r="A223" s="28" t="s">
+      <c r="A223" s="25" t="s">
         <v>261</v>
       </c>
-      <c r="B223" s="33" t="s">
+      <c r="B223" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="C223" s="30" t="s">
+      <c r="C223" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D223" s="31" t="s">
+      <c r="D223" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E223" s="32">
+      <c r="E223" s="62">
         <v>46022</v>
       </c>
       <c r="F223" s="15">
@@ -20989,19 +20990,19 @@
       </c>
     </row>
     <row r="224" spans="1:25" ht="38.25">
-      <c r="A224" s="22" t="s">
+      <c r="A224" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="B224" s="34" t="s">
+      <c r="B224" s="30" t="s">
         <v>236</v>
       </c>
-      <c r="C224" s="24" t="s">
+      <c r="C224" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D224" s="31" t="s">
+      <c r="D224" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E224" s="26">
+      <c r="E224" s="61">
         <v>46022</v>
       </c>
       <c r="F224" s="15">
@@ -21066,19 +21067,19 @@
       </c>
     </row>
     <row r="225" spans="1:25" ht="38.25">
-      <c r="A225" s="28" t="s">
+      <c r="A225" s="25" t="s">
         <v>263</v>
       </c>
-      <c r="B225" s="33" t="s">
+      <c r="B225" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="C225" s="30" t="s">
+      <c r="C225" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D225" s="31" t="s">
+      <c r="D225" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E225" s="32">
+      <c r="E225" s="62">
         <v>46022</v>
       </c>
       <c r="F225" s="15">
@@ -21143,19 +21144,19 @@
       </c>
     </row>
     <row r="226" spans="1:25" ht="38.25">
-      <c r="A226" s="22" t="s">
+      <c r="A226" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="B226" s="34" t="s">
+      <c r="B226" s="30" t="s">
         <v>236</v>
       </c>
-      <c r="C226" s="24" t="s">
+      <c r="C226" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D226" s="31" t="s">
+      <c r="D226" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E226" s="26">
+      <c r="E226" s="61">
         <v>46022</v>
       </c>
       <c r="F226" s="15">
@@ -21220,17 +21221,17 @@
       </c>
     </row>
     <row r="227" spans="1:25" ht="38.25">
-      <c r="A227" s="28" t="s">
+      <c r="A227" s="25" t="s">
         <v>265</v>
       </c>
-      <c r="B227" s="33" t="s">
+      <c r="B227" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="C227" s="30" t="s">
+      <c r="C227" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D227" s="31"/>
-      <c r="E227" s="32"/>
+      <c r="D227" s="28"/>
+      <c r="E227" s="62"/>
       <c r="F227" s="15">
         <v>4.25</v>
       </c>
@@ -21293,19 +21294,19 @@
       </c>
     </row>
     <row r="228" spans="1:25" ht="38.25">
-      <c r="A228" s="22" t="s">
+      <c r="A228" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="B228" s="34" t="s">
+      <c r="B228" s="30" t="s">
         <v>236</v>
       </c>
-      <c r="C228" s="24" t="s">
+      <c r="C228" s="22" t="s">
         <v>25</v>
       </c>
       <c r="D228" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E228" s="26"/>
+      <c r="E228" s="61"/>
       <c r="F228" s="15">
         <v>4.25</v>
       </c>
@@ -21375,10 +21376,10 @@
       <c r="C229" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D229" s="31" t="s">
+      <c r="D229" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="E229" s="21"/>
+      <c r="E229" s="59"/>
       <c r="F229" s="15">
         <v>4.25</v>
       </c>
@@ -21441,17 +21442,17 @@
       </c>
     </row>
     <row r="230" spans="1:25" ht="38.25">
-      <c r="A230" s="22" t="s">
+      <c r="A230" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="B230" s="23"/>
-      <c r="C230" s="24" t="s">
+      <c r="B230" s="21"/>
+      <c r="C230" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D230" s="31" t="s">
+      <c r="D230" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E230" s="26">
+      <c r="E230" s="61">
         <v>46022</v>
       </c>
       <c r="F230" s="15">
@@ -21516,17 +21517,17 @@
       </c>
     </row>
     <row r="231" spans="1:25" ht="38.25">
-      <c r="A231" s="28" t="s">
+      <c r="A231" s="25" t="s">
         <v>269</v>
       </c>
-      <c r="B231" s="29"/>
-      <c r="C231" s="30" t="s">
+      <c r="B231" s="26"/>
+      <c r="C231" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D231" s="31" t="s">
+      <c r="D231" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E231" s="32">
+      <c r="E231" s="62">
         <v>46022</v>
       </c>
       <c r="F231" s="15">
@@ -21591,17 +21592,17 @@
       </c>
     </row>
     <row r="232" spans="1:25" ht="38.25">
-      <c r="A232" s="22" t="s">
+      <c r="A232" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="B232" s="23"/>
-      <c r="C232" s="24" t="s">
+      <c r="B232" s="21"/>
+      <c r="C232" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D232" s="31" t="s">
+      <c r="D232" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E232" s="26">
+      <c r="E232" s="61">
         <v>46022</v>
       </c>
       <c r="F232" s="15">
@@ -21666,17 +21667,17 @@
       </c>
     </row>
     <row r="233" spans="1:25" ht="20.25">
-      <c r="A233" s="28" t="s">
+      <c r="A233" s="25" t="s">
         <v>271</v>
       </c>
-      <c r="B233" s="29"/>
-      <c r="C233" s="30" t="s">
+      <c r="B233" s="26"/>
+      <c r="C233" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D233" s="31" t="s">
+      <c r="D233" s="28" t="s">
         <v>238</v>
       </c>
-      <c r="E233" s="32"/>
+      <c r="E233" s="62"/>
       <c r="F233" s="15">
         <v>4.25</v>
       </c>
@@ -21742,7 +21743,7 @@
       <c r="A234" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="B234" s="35" t="s">
+      <c r="B234" s="31" t="s">
         <v>236</v>
       </c>
       <c r="C234" s="18" t="s">
@@ -21751,7 +21752,7 @@
       <c r="D234" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E234" s="20">
+      <c r="E234" s="60">
         <v>45973</v>
       </c>
       <c r="F234" s="15">
@@ -21826,7 +21827,7 @@
       <c r="D235" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E235" s="21">
+      <c r="E235" s="59">
         <v>45936</v>
       </c>
       <c r="F235" s="15">
@@ -21901,7 +21902,7 @@
       <c r="D236" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E236" s="20"/>
+      <c r="E236" s="60"/>
       <c r="F236" s="15">
         <v>4.25</v>
       </c>
@@ -21974,7 +21975,7 @@
       <c r="D237" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E237" s="21"/>
+      <c r="E237" s="59"/>
       <c r="F237" s="15">
         <v>4.25</v>
       </c>
@@ -22047,7 +22048,7 @@
       <c r="D238" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E238" s="20"/>
+      <c r="E238" s="60"/>
       <c r="F238" s="15">
         <v>4.25</v>
       </c>
@@ -22120,7 +22121,7 @@
       <c r="D239" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E239" s="21"/>
+      <c r="E239" s="59"/>
       <c r="F239" s="15">
         <v>4.25</v>
       </c>
@@ -22193,7 +22194,7 @@
       <c r="D240" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E240" s="20"/>
+      <c r="E240" s="60"/>
       <c r="F240" s="15">
         <v>4.25</v>
       </c>
@@ -22266,7 +22267,7 @@
       <c r="D241" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E241" s="21"/>
+      <c r="E241" s="59"/>
       <c r="F241" s="15">
         <v>4.25</v>
       </c>
@@ -22339,7 +22340,7 @@
       <c r="D242" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E242" s="20"/>
+      <c r="E242" s="60"/>
       <c r="F242" s="15">
         <v>4.25</v>
       </c>
@@ -22412,7 +22413,7 @@
       <c r="D243" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E243" s="21"/>
+      <c r="E243" s="59"/>
       <c r="F243" s="15">
         <v>4.25</v>
       </c>
@@ -22485,7 +22486,7 @@
       <c r="D244" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E244" s="20"/>
+      <c r="E244" s="60"/>
       <c r="F244" s="15">
         <v>4.25</v>
       </c>
@@ -22558,7 +22559,7 @@
       <c r="D245" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E245" s="21"/>
+      <c r="E245" s="59"/>
       <c r="F245" s="15">
         <v>4.25</v>
       </c>
@@ -22631,7 +22632,7 @@
       <c r="D246" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E246" s="20"/>
+      <c r="E246" s="60"/>
       <c r="F246" s="15">
         <v>4.25</v>
       </c>
@@ -22704,7 +22705,7 @@
       <c r="D247" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E247" s="21"/>
+      <c r="E247" s="59"/>
       <c r="F247" s="15">
         <v>4.25</v>
       </c>
@@ -22777,7 +22778,7 @@
       <c r="D248" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E248" s="20"/>
+      <c r="E248" s="60"/>
       <c r="F248" s="15">
         <v>4.25</v>
       </c>
@@ -22850,7 +22851,7 @@
       <c r="D249" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E249" s="21"/>
+      <c r="E249" s="59"/>
       <c r="F249" s="15">
         <v>4.25</v>
       </c>
@@ -22923,7 +22924,7 @@
       <c r="D250" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E250" s="20"/>
+      <c r="E250" s="60"/>
       <c r="F250" s="15">
         <v>4.25</v>
       </c>
@@ -22996,7 +22997,7 @@
       <c r="D251" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E251" s="21"/>
+      <c r="E251" s="59"/>
       <c r="F251" s="15">
         <v>4.25</v>
       </c>
@@ -23069,7 +23070,7 @@
       <c r="D252" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E252" s="20"/>
+      <c r="E252" s="60"/>
       <c r="F252" s="15">
         <v>4.25</v>
       </c>
@@ -23142,7 +23143,7 @@
       <c r="D253" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E253" s="21"/>
+      <c r="E253" s="59"/>
       <c r="F253" s="15">
         <v>4.25</v>
       </c>
@@ -23215,7 +23216,7 @@
       <c r="D254" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E254" s="20"/>
+      <c r="E254" s="60"/>
       <c r="F254" s="15">
         <v>4.25</v>
       </c>
@@ -23288,7 +23289,7 @@
       <c r="D255" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E255" s="21"/>
+      <c r="E255" s="59"/>
       <c r="F255" s="15">
         <v>4.25</v>
       </c>
@@ -23361,7 +23362,7 @@
       <c r="D256" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E256" s="20"/>
+      <c r="E256" s="60"/>
       <c r="F256" s="15">
         <v>4.25</v>
       </c>
@@ -23434,7 +23435,7 @@
       <c r="D257" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E257" s="21"/>
+      <c r="E257" s="59"/>
       <c r="F257" s="15">
         <v>4.25</v>
       </c>
@@ -23507,7 +23508,7 @@
       <c r="D258" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E258" s="20"/>
+      <c r="E258" s="60"/>
       <c r="F258" s="15">
         <v>4.25</v>
       </c>
@@ -23577,10 +23578,10 @@
       <c r="C259" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D259" s="31" t="s">
+      <c r="D259" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E259" s="21">
+      <c r="E259" s="59">
         <v>46022</v>
       </c>
       <c r="F259" s="15">
@@ -23655,7 +23656,7 @@
       <c r="D260" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="E260" s="20">
+      <c r="E260" s="60">
         <v>46022</v>
       </c>
       <c r="F260" s="15">
@@ -23730,7 +23731,7 @@
       <c r="D261" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E261" s="21"/>
+      <c r="E261" s="59"/>
       <c r="F261" s="15">
         <v>4.25</v>
       </c>
@@ -23803,7 +23804,7 @@
       <c r="D262" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E262" s="20"/>
+      <c r="E262" s="60"/>
       <c r="F262" s="15">
         <v>4.25</v>
       </c>
@@ -23876,7 +23877,7 @@
       <c r="D263" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E263" s="21"/>
+      <c r="E263" s="59"/>
       <c r="F263" s="15">
         <v>4.25</v>
       </c>
@@ -23949,7 +23950,7 @@
       <c r="D264" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E264" s="20"/>
+      <c r="E264" s="60"/>
       <c r="F264" s="15">
         <v>4.25</v>
       </c>
@@ -24022,7 +24023,7 @@
       <c r="D265" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E265" s="21"/>
+      <c r="E265" s="59"/>
       <c r="F265" s="15">
         <v>4.25</v>
       </c>
@@ -24095,7 +24096,7 @@
       <c r="D266" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E266" s="20"/>
+      <c r="E266" s="60"/>
       <c r="F266" s="15">
         <v>4.25</v>
       </c>
@@ -24165,10 +24166,10 @@
       <c r="C267" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D267" s="31" t="s">
+      <c r="D267" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E267" s="21">
+      <c r="E267" s="59">
         <v>46022</v>
       </c>
       <c r="F267" s="15">
@@ -24243,7 +24244,7 @@
       <c r="D268" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E268" s="20"/>
+      <c r="E268" s="60"/>
       <c r="F268" s="15">
         <v>4.25</v>
       </c>
@@ -24316,7 +24317,7 @@
       <c r="D269" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E269" s="21"/>
+      <c r="E269" s="59"/>
       <c r="F269" s="15">
         <v>4.25</v>
       </c>
@@ -24391,7 +24392,7 @@
       <c r="D270" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E270" s="20"/>
+      <c r="E270" s="60"/>
       <c r="F270" s="15">
         <v>4.25</v>
       </c>
@@ -24464,7 +24465,7 @@
       <c r="D271" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E271" s="21"/>
+      <c r="E271" s="59"/>
       <c r="F271" s="15">
         <v>4.25</v>
       </c>
@@ -24537,7 +24538,7 @@
       <c r="D272" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="E272" s="20">
+      <c r="E272" s="60">
         <v>46022</v>
       </c>
       <c r="F272" s="15">
@@ -24612,7 +24613,7 @@
       <c r="D273" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E273" s="21"/>
+      <c r="E273" s="59"/>
       <c r="F273" s="15">
         <v>4.25</v>
       </c>
@@ -24685,7 +24686,7 @@
       <c r="D274" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E274" s="20"/>
+      <c r="E274" s="60"/>
       <c r="F274" s="15">
         <v>4.25</v>
       </c>
@@ -24758,7 +24759,7 @@
       <c r="D275" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E275" s="21"/>
+      <c r="E275" s="59"/>
       <c r="F275" s="15">
         <v>4.25</v>
       </c>
@@ -24831,7 +24832,7 @@
       <c r="D276" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E276" s="20"/>
+      <c r="E276" s="60"/>
       <c r="F276" s="15">
         <v>4.25</v>
       </c>
@@ -24904,7 +24905,7 @@
       <c r="D277" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E277" s="21"/>
+      <c r="E277" s="59"/>
       <c r="F277" s="15">
         <v>4.25</v>
       </c>
@@ -24977,7 +24978,7 @@
       <c r="D278" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E278" s="20"/>
+      <c r="E278" s="60"/>
       <c r="F278" s="15">
         <v>4.25</v>
       </c>
@@ -25050,7 +25051,7 @@
       <c r="D279" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E279" s="21"/>
+      <c r="E279" s="59"/>
       <c r="F279" s="15">
         <v>4.25</v>
       </c>
@@ -25123,7 +25124,7 @@
       <c r="D280" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E280" s="20"/>
+      <c r="E280" s="60"/>
       <c r="F280" s="15">
         <v>4.25</v>
       </c>
@@ -25196,7 +25197,7 @@
       <c r="D281" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E281" s="21"/>
+      <c r="E281" s="59"/>
       <c r="F281" s="15">
         <v>4.25</v>
       </c>
@@ -25269,7 +25270,7 @@
       <c r="D282" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E282" s="20"/>
+      <c r="E282" s="60"/>
       <c r="F282" s="15">
         <v>4.25</v>
       </c>
@@ -25342,7 +25343,7 @@
       <c r="D283" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E283" s="21"/>
+      <c r="E283" s="59"/>
       <c r="F283" s="15">
         <v>4.25</v>
       </c>
@@ -25415,7 +25416,7 @@
       <c r="D284" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E284" s="20"/>
+      <c r="E284" s="60"/>
       <c r="F284" s="15">
         <v>4.25</v>
       </c>
@@ -25488,7 +25489,7 @@
       <c r="D285" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E285" s="21"/>
+      <c r="E285" s="59"/>
       <c r="F285" s="15">
         <v>4.25</v>
       </c>
@@ -25561,7 +25562,7 @@
       <c r="D286" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E286" s="20"/>
+      <c r="E286" s="60"/>
       <c r="F286" s="15">
         <v>4.25</v>
       </c>
@@ -25634,7 +25635,7 @@
       <c r="D287" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E287" s="21"/>
+      <c r="E287" s="59"/>
       <c r="F287" s="15">
         <v>4.25</v>
       </c>
@@ -25707,7 +25708,7 @@
       <c r="D288" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="E288" s="20">
+      <c r="E288" s="60">
         <v>46022</v>
       </c>
       <c r="F288" s="15">
@@ -25782,7 +25783,7 @@
       <c r="D289" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E289" s="21"/>
+      <c r="E289" s="59"/>
       <c r="F289" s="15">
         <v>4.25</v>
       </c>
@@ -25855,7 +25856,7 @@
       <c r="D290" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E290" s="20"/>
+      <c r="E290" s="60"/>
       <c r="F290" s="15">
         <v>4.25</v>
       </c>
@@ -25928,7 +25929,7 @@
       <c r="D291" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E291" s="21"/>
+      <c r="E291" s="59"/>
       <c r="F291" s="15">
         <v>4.25</v>
       </c>
@@ -26001,7 +26002,7 @@
       <c r="D292" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E292" s="20"/>
+      <c r="E292" s="60"/>
       <c r="F292" s="15">
         <v>4.25</v>
       </c>
@@ -26074,7 +26075,7 @@
       <c r="D293" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E293" s="21"/>
+      <c r="E293" s="59"/>
       <c r="F293" s="15">
         <v>4.25</v>
       </c>
@@ -26147,7 +26148,7 @@
       <c r="D294" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E294" s="20"/>
+      <c r="E294" s="60"/>
       <c r="F294" s="15">
         <v>4.25</v>
       </c>
@@ -26220,7 +26221,7 @@
       <c r="D295" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E295" s="21"/>
+      <c r="E295" s="59"/>
       <c r="F295" s="15">
         <v>4.25</v>
       </c>
@@ -26293,7 +26294,7 @@
       <c r="D296" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E296" s="20"/>
+      <c r="E296" s="60"/>
       <c r="F296" s="15">
         <v>4.25</v>
       </c>
@@ -26366,7 +26367,7 @@
       <c r="D297" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E297" s="21"/>
+      <c r="E297" s="59"/>
       <c r="F297" s="15">
         <v>4.25</v>
       </c>
@@ -26439,7 +26440,7 @@
       <c r="D298" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E298" s="20"/>
+      <c r="E298" s="60"/>
       <c r="F298" s="15">
         <v>4.25</v>
       </c>
@@ -26512,7 +26513,7 @@
       <c r="D299" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E299" s="21"/>
+      <c r="E299" s="59"/>
       <c r="F299" s="15">
         <v>4.25</v>
       </c>
@@ -26585,7 +26586,7 @@
       <c r="D300" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E300" s="20"/>
+      <c r="E300" s="60"/>
       <c r="F300" s="15">
         <v>4.25</v>
       </c>
@@ -26658,7 +26659,7 @@
       <c r="D301" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E301" s="21"/>
+      <c r="E301" s="59"/>
       <c r="F301" s="15">
         <v>4.25</v>
       </c>
@@ -26731,7 +26732,7 @@
       <c r="D302" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E302" s="20"/>
+      <c r="E302" s="60"/>
       <c r="F302" s="15">
         <v>4.25</v>
       </c>
@@ -26804,7 +26805,7 @@
       <c r="D303" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E303" s="21"/>
+      <c r="E303" s="59"/>
       <c r="F303" s="15">
         <v>4.25</v>
       </c>
@@ -26877,7 +26878,7 @@
       <c r="D304" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E304" s="20"/>
+      <c r="E304" s="60"/>
       <c r="F304" s="15">
         <v>4.25</v>
       </c>
@@ -26950,7 +26951,7 @@
       <c r="D305" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E305" s="21"/>
+      <c r="E305" s="59"/>
       <c r="F305" s="15">
         <v>4.25</v>
       </c>
@@ -27023,7 +27024,7 @@
       <c r="D306" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E306" s="20"/>
+      <c r="E306" s="60"/>
       <c r="F306" s="15">
         <v>4.25</v>
       </c>
@@ -27096,7 +27097,7 @@
       <c r="D307" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E307" s="21"/>
+      <c r="E307" s="59"/>
       <c r="F307" s="15">
         <v>4.25</v>
       </c>
@@ -27169,7 +27170,7 @@
       <c r="D308" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E308" s="20"/>
+      <c r="E308" s="60"/>
       <c r="F308" s="15">
         <v>4.25</v>
       </c>
@@ -27242,7 +27243,7 @@
       <c r="D309" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E309" s="21"/>
+      <c r="E309" s="59"/>
       <c r="F309" s="15">
         <v>4.25</v>
       </c>
@@ -27315,7 +27316,7 @@
       <c r="D310" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E310" s="20"/>
+      <c r="E310" s="60"/>
       <c r="F310" s="15">
         <v>4.25</v>
       </c>
@@ -27388,7 +27389,7 @@
       <c r="D311" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E311" s="21"/>
+      <c r="E311" s="59"/>
       <c r="F311" s="15">
         <v>4.25</v>
       </c>
@@ -27461,7 +27462,7 @@
       <c r="D312" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E312" s="20"/>
+      <c r="E312" s="60"/>
       <c r="F312" s="15">
         <v>4.25</v>
       </c>
@@ -27534,7 +27535,7 @@
       <c r="D313" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E313" s="21"/>
+      <c r="E313" s="59"/>
       <c r="F313" s="15">
         <v>4.25</v>
       </c>
@@ -27607,7 +27608,7 @@
       <c r="D314" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E314" s="20"/>
+      <c r="E314" s="60"/>
       <c r="F314" s="15">
         <v>4.25</v>
       </c>
@@ -27680,7 +27681,7 @@
       <c r="D315" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E315" s="21"/>
+      <c r="E315" s="59"/>
       <c r="F315" s="15">
         <v>4.25</v>
       </c>
@@ -27753,7 +27754,7 @@
       <c r="D316" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E316" s="20"/>
+      <c r="E316" s="60"/>
       <c r="F316" s="15">
         <v>4.25</v>
       </c>
@@ -27826,7 +27827,7 @@
       <c r="D317" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E317" s="21"/>
+      <c r="E317" s="59"/>
       <c r="F317" s="15">
         <v>4.25</v>
       </c>
@@ -27899,7 +27900,7 @@
       <c r="D318" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E318" s="20"/>
+      <c r="E318" s="60"/>
       <c r="F318" s="15">
         <v>4.25</v>
       </c>
@@ -27972,7 +27973,7 @@
       <c r="D319" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E319" s="21"/>
+      <c r="E319" s="59"/>
       <c r="F319" s="15">
         <v>4.25</v>
       </c>
@@ -28045,7 +28046,7 @@
       <c r="D320" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E320" s="20"/>
+      <c r="E320" s="60"/>
       <c r="F320" s="15">
         <v>4.25</v>
       </c>
@@ -28118,7 +28119,7 @@
       <c r="D321" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E321" s="21"/>
+      <c r="E321" s="59"/>
       <c r="F321" s="15">
         <v>4.25</v>
       </c>
@@ -28191,7 +28192,7 @@
       <c r="D322" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E322" s="20"/>
+      <c r="E322" s="60"/>
       <c r="F322" s="15">
         <v>4.25</v>
       </c>
@@ -28264,7 +28265,7 @@
       <c r="D323" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E323" s="21"/>
+      <c r="E323" s="59"/>
       <c r="F323" s="15">
         <v>4.25</v>
       </c>
@@ -28337,7 +28338,7 @@
       <c r="D324" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E324" s="20"/>
+      <c r="E324" s="60"/>
       <c r="F324" s="15">
         <v>4.25</v>
       </c>
@@ -28410,7 +28411,7 @@
       <c r="D325" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E325" s="21"/>
+      <c r="E325" s="59"/>
       <c r="F325" s="15">
         <v>4.25</v>
       </c>
@@ -28483,7 +28484,7 @@
       <c r="D326" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E326" s="20"/>
+      <c r="E326" s="60"/>
       <c r="F326" s="15">
         <v>4.25</v>
       </c>
@@ -28556,7 +28557,7 @@
       <c r="D327" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E327" s="21"/>
+      <c r="E327" s="59"/>
       <c r="F327" s="15">
         <v>4.25</v>
       </c>
@@ -28629,7 +28630,7 @@
       <c r="D328" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E328" s="20"/>
+      <c r="E328" s="60"/>
       <c r="F328" s="15">
         <v>4.25</v>
       </c>
@@ -28702,7 +28703,7 @@
       <c r="D329" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E329" s="21"/>
+      <c r="E329" s="59"/>
       <c r="F329" s="15">
         <v>4.25</v>
       </c>
@@ -28775,7 +28776,7 @@
       <c r="D330" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E330" s="20"/>
+      <c r="E330" s="60"/>
       <c r="F330" s="15">
         <v>4.25</v>
       </c>
@@ -28848,7 +28849,7 @@
       <c r="D331" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E331" s="21"/>
+      <c r="E331" s="59"/>
       <c r="F331" s="15">
         <v>4.25</v>
       </c>
@@ -28918,10 +28919,10 @@
       <c r="C332" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D332" s="31" t="s">
+      <c r="D332" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E332" s="20">
+      <c r="E332" s="60">
         <v>46022</v>
       </c>
       <c r="F332" s="15">
@@ -28996,7 +28997,7 @@
       <c r="D333" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E333" s="21"/>
+      <c r="E333" s="59"/>
       <c r="F333" s="15">
         <v>4.25</v>
       </c>
@@ -29069,7 +29070,7 @@
       <c r="D334" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E334" s="20"/>
+      <c r="E334" s="60"/>
       <c r="F334" s="15">
         <v>4.25</v>
       </c>
@@ -29142,7 +29143,7 @@
       <c r="D335" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E335" s="21"/>
+      <c r="E335" s="59"/>
       <c r="F335" s="15">
         <v>4.25</v>
       </c>
@@ -29212,10 +29213,10 @@
       <c r="C336" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D336" s="31" t="s">
+      <c r="D336" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E336" s="20">
+      <c r="E336" s="60">
         <v>46022</v>
       </c>
       <c r="F336" s="15">
@@ -29290,7 +29291,7 @@
       <c r="D337" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E337" s="21"/>
+      <c r="E337" s="59"/>
       <c r="F337" s="15">
         <v>4.25</v>
       </c>
@@ -29363,7 +29364,7 @@
       <c r="D338" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E338" s="20"/>
+      <c r="E338" s="60"/>
       <c r="F338" s="15">
         <v>4.25</v>
       </c>
@@ -29426,17 +29427,17 @@
       </c>
     </row>
     <row r="339" spans="1:25" ht="20.25">
-      <c r="A339" s="28" t="s">
+      <c r="A339" s="25" t="s">
         <v>377</v>
       </c>
-      <c r="B339" s="29"/>
-      <c r="C339" s="30" t="s">
+      <c r="B339" s="26"/>
+      <c r="C339" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="D339" s="31" t="s">
+      <c r="D339" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="E339" s="32"/>
+      <c r="E339" s="62"/>
       <c r="F339" s="15">
         <v>4.25</v>
       </c>
@@ -29509,7 +29510,7 @@
       <c r="D340" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E340" s="20"/>
+      <c r="E340" s="60"/>
       <c r="F340" s="15">
         <v>4.25</v>
       </c>
@@ -29572,17 +29573,17 @@
       </c>
     </row>
     <row r="341" spans="1:25" ht="20.25">
-      <c r="A341" s="28" t="s">
+      <c r="A341" s="25" t="s">
         <v>379</v>
       </c>
-      <c r="B341" s="29"/>
-      <c r="C341" s="30" t="s">
+      <c r="B341" s="26"/>
+      <c r="C341" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="D341" s="31" t="s">
+      <c r="D341" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="E341" s="32"/>
+      <c r="E341" s="62"/>
       <c r="F341" s="15">
         <v>4.25</v>
       </c>
@@ -29645,17 +29646,17 @@
       </c>
     </row>
     <row r="342" spans="1:25" ht="20.25">
-      <c r="A342" s="22" t="s">
+      <c r="A342" s="20" t="s">
         <v>380</v>
       </c>
-      <c r="B342" s="23"/>
-      <c r="C342" s="24" t="s">
+      <c r="B342" s="21"/>
+      <c r="C342" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="D342" s="25" t="s">
+      <c r="D342" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="E342" s="26"/>
+      <c r="E342" s="61"/>
       <c r="F342" s="15">
         <v>4.25</v>
       </c>
@@ -29718,17 +29719,17 @@
       </c>
     </row>
     <row r="343" spans="1:25" ht="20.25">
-      <c r="A343" s="36" t="s">
+      <c r="A343" s="32" t="s">
         <v>381</v>
       </c>
-      <c r="B343" s="37"/>
-      <c r="C343" s="38" t="s">
+      <c r="B343" s="33"/>
+      <c r="C343" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="D343" s="39" t="s">
+      <c r="D343" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="E343" s="67"/>
+      <c r="E343" s="63"/>
       <c r="F343" s="15">
         <v>4.25</v>
       </c>
@@ -29791,17 +29792,17 @@
       </c>
     </row>
     <row r="344" spans="1:25" ht="20.25">
-      <c r="A344" s="22" t="s">
+      <c r="A344" s="20" t="s">
         <v>382</v>
       </c>
-      <c r="B344" s="23"/>
-      <c r="C344" s="24" t="s">
+      <c r="B344" s="21"/>
+      <c r="C344" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="D344" s="25" t="s">
+      <c r="D344" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="E344" s="26"/>
+      <c r="E344" s="61"/>
       <c r="F344" s="15">
         <v>4.25</v>
       </c>
@@ -29864,17 +29865,17 @@
       </c>
     </row>
     <row r="345" spans="1:25" ht="20.25">
-      <c r="A345" s="28" t="s">
+      <c r="A345" s="25" t="s">
         <v>383</v>
       </c>
-      <c r="B345" s="29"/>
-      <c r="C345" s="30" t="s">
+      <c r="B345" s="26"/>
+      <c r="C345" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="D345" s="31" t="s">
+      <c r="D345" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="E345" s="32"/>
+      <c r="E345" s="62"/>
       <c r="F345" s="15">
         <v>4.25</v>
       </c>
@@ -29940,16 +29941,16 @@
       <c r="A346" s="16" t="s">
         <v>384</v>
       </c>
-      <c r="B346" s="35" t="s">
+      <c r="B346" s="31" t="s">
         <v>385</v>
       </c>
       <c r="C346" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D346" s="31" t="s">
+      <c r="D346" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E346" s="20">
+      <c r="E346" s="60">
         <v>46022</v>
       </c>
       <c r="F346" s="15">
@@ -30014,17 +30015,17 @@
       </c>
     </row>
     <row r="347" spans="1:25" ht="20.25">
-      <c r="A347" s="28" t="s">
+      <c r="A347" s="25" t="s">
         <v>386</v>
       </c>
-      <c r="B347" s="33"/>
-      <c r="C347" s="30" t="s">
+      <c r="B347" s="29"/>
+      <c r="C347" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D347" s="31" t="s">
+      <c r="D347" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="E347" s="32"/>
+      <c r="E347" s="62"/>
       <c r="F347" s="15">
         <v>4.25</v>
       </c>
@@ -30090,7 +30091,7 @@
       <c r="A348" s="16" t="s">
         <v>387</v>
       </c>
-      <c r="B348" s="35" t="s">
+      <c r="B348" s="31" t="s">
         <v>388</v>
       </c>
       <c r="C348" s="18" t="s">
@@ -30099,7 +30100,7 @@
       <c r="D348" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E348" s="20"/>
+      <c r="E348" s="60"/>
       <c r="F348" s="15">
         <v>4.25</v>
       </c>
@@ -30162,17 +30163,17 @@
       </c>
     </row>
     <row r="349" spans="1:25" ht="20.25">
-      <c r="A349" s="28" t="s">
+      <c r="A349" s="25" t="s">
         <v>389</v>
       </c>
-      <c r="B349" s="33"/>
-      <c r="C349" s="30" t="s">
+      <c r="B349" s="29"/>
+      <c r="C349" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="D349" s="31" t="s">
+      <c r="D349" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="E349" s="32"/>
+      <c r="E349" s="62"/>
       <c r="F349" s="15">
         <v>4.25</v>
       </c>
@@ -30238,12 +30239,12 @@
       <c r="A350" s="16" t="s">
         <v>390</v>
       </c>
-      <c r="B350" s="35"/>
+      <c r="B350" s="31"/>
       <c r="C350" s="18" t="s">
         <v>35</v>
       </c>
       <c r="D350" s="19"/>
-      <c r="E350" s="20"/>
+      <c r="E350" s="60"/>
       <c r="F350" s="15">
         <v>4.25</v>
       </c>
@@ -30306,17 +30307,17 @@
       </c>
     </row>
     <row r="351" spans="1:25" ht="20.25">
-      <c r="A351" s="28" t="s">
+      <c r="A351" s="25" t="s">
         <v>391</v>
       </c>
-      <c r="B351" s="33"/>
-      <c r="C351" s="30" t="s">
+      <c r="B351" s="29"/>
+      <c r="C351" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="D351" s="31" t="s">
+      <c r="D351" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="E351" s="32"/>
+      <c r="E351" s="62"/>
       <c r="F351" s="15">
         <v>4.25</v>
       </c>
@@ -30379,19 +30380,19 @@
       </c>
     </row>
     <row r="352" spans="1:25" ht="20.25">
-      <c r="A352" s="28" t="s">
+      <c r="A352" s="25" t="s">
         <v>392</v>
       </c>
-      <c r="B352" s="33" t="s">
+      <c r="B352" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="C352" s="30" t="s">
+      <c r="C352" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="D352" s="31" t="s">
+      <c r="D352" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="E352" s="32"/>
+      <c r="E352" s="62"/>
       <c r="F352" s="15">
         <v>4.25</v>
       </c>
@@ -30454,17 +30455,17 @@
       </c>
     </row>
     <row r="353" spans="1:25" ht="25.5">
-      <c r="A353" s="40" t="s">
+      <c r="A353" s="36" t="s">
         <v>393</v>
       </c>
-      <c r="B353" s="40"/>
-      <c r="C353" s="41" t="s">
+      <c r="B353" s="36"/>
+      <c r="C353" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="D353" s="42" t="s">
+      <c r="D353" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="E353" s="68"/>
+      <c r="E353" s="64"/>
       <c r="F353" s="15">
         <v>4.25</v>
       </c>
@@ -30533,13 +30534,13 @@
       <c r="B354" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C354" s="43" t="s">
+      <c r="C354" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D354" s="44" t="s">
+      <c r="D354" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="E354" s="60"/>
+      <c r="E354" s="65"/>
       <c r="F354" s="15">
         <v>4.25</v>
       </c>
@@ -30602,17 +30603,17 @@
       </c>
     </row>
     <row r="355" spans="1:25" ht="25.5">
-      <c r="A355" s="40" t="s">
+      <c r="A355" s="36" t="s">
         <v>395</v>
       </c>
-      <c r="B355" s="40"/>
-      <c r="C355" s="41" t="s">
+      <c r="B355" s="36"/>
+      <c r="C355" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="D355" s="42" t="s">
+      <c r="D355" s="38" t="s">
         <v>238</v>
       </c>
-      <c r="E355" s="69"/>
+      <c r="E355" s="66"/>
       <c r="F355" s="15">
         <v>4.25</v>
       </c>
@@ -30679,13 +30680,13 @@
         <v>396</v>
       </c>
       <c r="B356" s="1"/>
-      <c r="C356" s="43" t="s">
+      <c r="C356" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D356" s="44" t="s">
+      <c r="D356" s="40" t="s">
         <v>238</v>
       </c>
-      <c r="E356" s="60"/>
+      <c r="E356" s="65"/>
       <c r="F356" s="15">
         <v>4.25</v>
       </c>
@@ -30748,17 +30749,17 @@
       </c>
     </row>
     <row r="357" spans="1:25" ht="20.25">
-      <c r="A357" s="40" t="s">
+      <c r="A357" s="36" t="s">
         <v>397</v>
       </c>
-      <c r="B357" s="40"/>
-      <c r="C357" s="41" t="s">
+      <c r="B357" s="36"/>
+      <c r="C357" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="D357" s="42" t="s">
+      <c r="D357" s="38" t="s">
         <v>238</v>
       </c>
-      <c r="E357" s="69"/>
+      <c r="E357" s="66"/>
       <c r="F357" s="15">
         <v>4.25</v>
       </c>
@@ -30825,13 +30826,13 @@
         <v>398</v>
       </c>
       <c r="B358" s="1"/>
-      <c r="C358" s="43" t="s">
+      <c r="C358" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D358" s="44" t="s">
+      <c r="D358" s="40" t="s">
         <v>238</v>
       </c>
-      <c r="E358" s="60"/>
+      <c r="E358" s="65"/>
       <c r="F358" s="15">
         <v>4.25</v>
       </c>
@@ -30894,17 +30895,17 @@
       </c>
     </row>
     <row r="359" spans="1:25" ht="38.25">
-      <c r="A359" s="45" t="s">
+      <c r="A359" s="41" t="s">
         <v>399</v>
       </c>
-      <c r="B359" s="45"/>
-      <c r="C359" s="46" t="s">
+      <c r="B359" s="41"/>
+      <c r="C359" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="D359" s="31" t="s">
+      <c r="D359" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E359" s="47">
+      <c r="E359" s="67">
         <v>46022</v>
       </c>
       <c r="F359" s="15">
@@ -30973,11 +30974,11 @@
         <v>400</v>
       </c>
       <c r="B360" s="1"/>
-      <c r="C360" s="48" t="s">
+      <c r="C360" s="43" t="s">
         <v>401</v>
       </c>
-      <c r="D360" s="44"/>
-      <c r="E360" s="60"/>
+      <c r="D360" s="40"/>
+      <c r="E360" s="65"/>
       <c r="F360" s="15">
         <v>4.25</v>
       </c>
@@ -31040,17 +31041,17 @@
       </c>
     </row>
     <row r="361" spans="1:25" ht="38.25">
-      <c r="A361" s="45" t="s">
+      <c r="A361" s="41" t="s">
         <v>402</v>
       </c>
-      <c r="B361" s="45"/>
-      <c r="C361" s="46" t="s">
+      <c r="B361" s="41"/>
+      <c r="C361" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="D361" s="31" t="s">
+      <c r="D361" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E361" s="47">
+      <c r="E361" s="67">
         <v>46022</v>
       </c>
       <c r="F361" s="15">
@@ -31115,17 +31116,17 @@
       </c>
     </row>
     <row r="362" spans="1:25" ht="38.25">
-      <c r="A362" s="49" t="s">
+      <c r="A362" s="44" t="s">
         <v>403</v>
       </c>
-      <c r="B362" s="49"/>
-      <c r="C362" s="50" t="s">
+      <c r="B362" s="44"/>
+      <c r="C362" s="45" t="s">
         <v>404</v>
       </c>
-      <c r="D362" s="31" t="s">
+      <c r="D362" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E362" s="51">
+      <c r="E362" s="68">
         <v>46022</v>
       </c>
       <c r="F362" s="15">
@@ -31190,17 +31191,17 @@
       </c>
     </row>
     <row r="363" spans="1:25" ht="25.5">
-      <c r="A363" s="40" t="s">
+      <c r="A363" s="36" t="s">
         <v>405</v>
       </c>
-      <c r="B363" s="40"/>
-      <c r="C363" s="41" t="s">
+      <c r="B363" s="36"/>
+      <c r="C363" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="D363" s="42" t="s">
+      <c r="D363" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="E363" s="69"/>
+      <c r="E363" s="66"/>
       <c r="F363" s="15">
         <v>4.25</v>
       </c>
@@ -31263,17 +31264,17 @@
       </c>
     </row>
     <row r="364" spans="1:25" ht="20.25">
-      <c r="A364" s="52" t="s">
+      <c r="A364" s="46" t="s">
         <v>406</v>
       </c>
-      <c r="B364" s="52"/>
-      <c r="C364" s="53" t="s">
+      <c r="B364" s="46"/>
+      <c r="C364" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="D364" s="54" t="s">
+      <c r="D364" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="E364" s="70"/>
+      <c r="E364" s="69"/>
       <c r="F364" s="15">
         <v>4.25</v>
       </c>
@@ -31336,17 +31337,17 @@
       </c>
     </row>
     <row r="365" spans="1:25" ht="20.25">
-      <c r="A365" s="40" t="s">
+      <c r="A365" s="36" t="s">
         <v>407</v>
       </c>
-      <c r="B365" s="40"/>
-      <c r="C365" s="41" t="s">
+      <c r="B365" s="36"/>
+      <c r="C365" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="D365" s="42" t="s">
+      <c r="D365" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="E365" s="69"/>
+      <c r="E365" s="66"/>
       <c r="F365" s="15">
         <v>4.25</v>
       </c>
@@ -31409,17 +31410,17 @@
       </c>
     </row>
     <row r="366" spans="1:25" ht="20.25">
-      <c r="A366" s="52" t="s">
+      <c r="A366" s="46" t="s">
         <v>408</v>
       </c>
-      <c r="B366" s="52"/>
-      <c r="C366" s="53" t="s">
+      <c r="B366" s="46"/>
+      <c r="C366" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="D366" s="54" t="s">
+      <c r="D366" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="E366" s="70"/>
+      <c r="E366" s="69"/>
       <c r="F366" s="15">
         <v>4.25</v>
       </c>
@@ -31482,17 +31483,17 @@
       </c>
     </row>
     <row r="367" spans="1:25" ht="20.25">
-      <c r="A367" s="45" t="s">
+      <c r="A367" s="41" t="s">
         <v>409</v>
       </c>
-      <c r="B367" s="45"/>
-      <c r="C367" s="55" t="s">
+      <c r="B367" s="41"/>
+      <c r="C367" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="D367" s="56" t="s">
+      <c r="D367" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="E367" s="47"/>
+      <c r="E367" s="67"/>
       <c r="F367" s="15">
         <v>4.25</v>
       </c>
@@ -31555,19 +31556,19 @@
       </c>
     </row>
     <row r="368" spans="1:25" ht="25.5">
-      <c r="A368" s="52" t="s">
+      <c r="A368" s="46" t="s">
         <v>410</v>
       </c>
-      <c r="B368" s="52" t="s">
+      <c r="B368" s="46" t="s">
         <v>411</v>
       </c>
-      <c r="C368" s="53" t="s">
+      <c r="C368" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="D368" s="54" t="s">
+      <c r="D368" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="E368" s="70"/>
+      <c r="E368" s="69"/>
       <c r="F368" s="15">
         <v>4.25</v>
       </c>
@@ -31630,17 +31631,17 @@
       </c>
     </row>
     <row r="369" spans="1:25" ht="38.25">
-      <c r="A369" s="45" t="s">
+      <c r="A369" s="41" t="s">
         <v>412</v>
       </c>
-      <c r="B369" s="45"/>
-      <c r="C369" s="55" t="s">
+      <c r="B369" s="41"/>
+      <c r="C369" s="49" t="s">
         <v>124</v>
       </c>
-      <c r="D369" s="31" t="s">
+      <c r="D369" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E369" s="47">
+      <c r="E369" s="67">
         <v>46022</v>
       </c>
       <c r="F369" s="15">
@@ -31705,15 +31706,15 @@
       </c>
     </row>
     <row r="370" spans="1:25" ht="20.25">
-      <c r="A370" s="52" t="s">
+      <c r="A370" s="46" t="s">
         <v>413</v>
       </c>
-      <c r="B370" s="52"/>
-      <c r="C370" s="52" t="s">
+      <c r="B370" s="46"/>
+      <c r="C370" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="D370" s="52"/>
-      <c r="E370" s="70"/>
+      <c r="D370" s="46"/>
+      <c r="E370" s="69"/>
       <c r="F370" s="15">
         <v>4.25</v>
       </c>
@@ -31776,17 +31777,17 @@
       </c>
     </row>
     <row r="371" spans="1:25" ht="38.25">
-      <c r="A371" s="57" t="s">
+      <c r="A371" s="51" t="s">
         <v>414</v>
       </c>
-      <c r="B371" s="57"/>
-      <c r="C371" s="58" t="s">
+      <c r="B371" s="51"/>
+      <c r="C371" s="52" t="s">
         <v>124</v>
       </c>
-      <c r="D371" s="31" t="s">
+      <c r="D371" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E371" s="59">
+      <c r="E371" s="70">
         <v>45967</v>
       </c>
       <c r="F371" s="15">
@@ -31855,13 +31856,13 @@
         <v>415</v>
       </c>
       <c r="B372" s="1"/>
-      <c r="C372" s="43" t="s">
+      <c r="C372" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D372" s="31" t="s">
+      <c r="D372" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E372" s="60">
+      <c r="E372" s="65">
         <v>46022</v>
       </c>
       <c r="F372" s="15">
@@ -31926,17 +31927,17 @@
       </c>
     </row>
     <row r="373" spans="1:25" ht="38.25">
-      <c r="A373" s="61" t="s">
+      <c r="A373" s="53" t="s">
         <v>416</v>
       </c>
-      <c r="B373" s="45"/>
-      <c r="C373" s="46" t="s">
+      <c r="B373" s="41"/>
+      <c r="C373" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="D373" s="31" t="s">
+      <c r="D373" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E373" s="47">
+      <c r="E373" s="67">
         <v>46022</v>
       </c>
       <c r="F373" s="15">
@@ -32005,13 +32006,13 @@
         <v>417</v>
       </c>
       <c r="B374" s="1"/>
-      <c r="C374" s="43" t="s">
+      <c r="C374" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D374" s="31" t="s">
+      <c r="D374" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E374" s="60">
+      <c r="E374" s="65">
         <v>46022</v>
       </c>
       <c r="F374" s="15">
@@ -32076,17 +32077,17 @@
       </c>
     </row>
     <row r="375" spans="1:25" ht="38.25">
-      <c r="A375" s="45" t="s">
+      <c r="A375" s="41" t="s">
         <v>418</v>
       </c>
-      <c r="B375" s="45"/>
-      <c r="C375" s="46" t="s">
+      <c r="B375" s="41"/>
+      <c r="C375" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="D375" s="54" t="s">
+      <c r="D375" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="E375" s="47">
+      <c r="E375" s="67">
         <v>46006</v>
       </c>
       <c r="F375" s="15">
@@ -32155,13 +32156,13 @@
         <v>419</v>
       </c>
       <c r="B376" s="1"/>
-      <c r="C376" s="43" t="s">
+      <c r="C376" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="D376" s="54" t="s">
+      <c r="D376" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="E376" s="60">
+      <c r="E376" s="65">
         <v>46022</v>
       </c>
       <c r="F376" s="15">
@@ -32226,17 +32227,17 @@
       </c>
     </row>
     <row r="377" spans="1:25" ht="20.25">
-      <c r="A377" s="45" t="s">
+      <c r="A377" s="41" t="s">
         <v>420</v>
       </c>
-      <c r="B377" s="45"/>
-      <c r="C377" s="46" t="s">
+      <c r="B377" s="41"/>
+      <c r="C377" s="42" t="s">
         <v>43</v>
       </c>
       <c r="D377" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E377" s="47"/>
+      <c r="E377" s="67"/>
       <c r="F377" s="15">
         <v>4.25</v>
       </c>
@@ -32299,17 +32300,17 @@
       </c>
     </row>
     <row r="378" spans="1:25" ht="20.25">
-      <c r="A378" s="52" t="s">
+      <c r="A378" s="46" t="s">
         <v>421</v>
       </c>
-      <c r="B378" s="52"/>
-      <c r="C378" s="43" t="s">
+      <c r="B378" s="46"/>
+      <c r="C378" s="39" t="s">
         <v>404</v>
       </c>
-      <c r="D378" s="54" t="s">
+      <c r="D378" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="E378" s="70"/>
+      <c r="E378" s="69"/>
       <c r="F378" s="15">
         <v>4.25</v>
       </c>
@@ -32372,17 +32373,17 @@
       </c>
     </row>
     <row r="379" spans="1:25" ht="30">
-      <c r="A379" s="57" t="s">
+      <c r="A379" s="51" t="s">
         <v>422</v>
       </c>
-      <c r="B379" s="57"/>
-      <c r="C379" s="46" t="s">
+      <c r="B379" s="51"/>
+      <c r="C379" s="42" t="s">
         <v>43</v>
       </c>
       <c r="D379" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="E379" s="59"/>
+      <c r="E379" s="70"/>
       <c r="F379" s="15">
         <v>4.25</v>
       </c>
@@ -32445,17 +32446,17 @@
       </c>
     </row>
     <row r="380" spans="1:25" ht="20.25">
-      <c r="A380" s="49" t="s">
+      <c r="A380" s="44" t="s">
         <v>423</v>
       </c>
-      <c r="B380" s="49"/>
-      <c r="C380" s="43" t="s">
+      <c r="B380" s="44"/>
+      <c r="C380" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D380" s="54" t="s">
+      <c r="D380" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="E380" s="51"/>
+      <c r="E380" s="68"/>
       <c r="F380" s="15">
         <v>4.25</v>
       </c>
@@ -32518,17 +32519,17 @@
       </c>
     </row>
     <row r="381" spans="1:25" ht="38.25">
-      <c r="A381" s="45" t="s">
+      <c r="A381" s="41" t="s">
         <v>424</v>
       </c>
-      <c r="B381" s="45"/>
-      <c r="C381" s="46" t="s">
+      <c r="B381" s="41"/>
+      <c r="C381" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="D381" s="42" t="s">
+      <c r="D381" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E381" s="47">
+      <c r="E381" s="67">
         <v>46022</v>
       </c>
       <c r="F381" s="15">
@@ -32597,13 +32598,13 @@
         <v>425</v>
       </c>
       <c r="B382" s="1"/>
-      <c r="C382" s="43" t="s">
+      <c r="C382" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D382" s="44" t="s">
+      <c r="D382" s="40" t="s">
         <v>238</v>
       </c>
-      <c r="E382" s="60"/>
+      <c r="E382" s="65"/>
       <c r="F382" s="15">
         <v>4.25</v>
       </c>
@@ -32667,12 +32668,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="T1:Y1"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="F1:K1"/>
     <mergeCell ref="L1:Q1"/>
     <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:Y1"/>
   </mergeCells>
   <conditionalFormatting sqref="A11:A14 A5:A9">
     <cfRule type="duplicateValues" dxfId="19" priority="19" stopIfTrue="1"/>
@@ -32735,6 +32736,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="8" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>